--- a/templates/hemodialysis_list_veícs_template.xlsx
+++ b/templates/hemodialysis_list_veícs_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{18843B92-6CCB-4C1B-BC9B-76BE8353557D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A9CC0C7-51D3-4F66-A72F-23C7ED3D68AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9FA8002F-7B96-42FD-9428-F3AD62B1682C}"/>
   </bookViews>
@@ -78,16 +78,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="10" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -375,132 +367,131 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+      <protection locked="0"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -529,10 +520,10 @@
       <xdr:rowOff>6350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>6350</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>267050</xdr:colOff>
       <xdr:row>4</xdr:row>
-      <xdr:rowOff>86237</xdr:rowOff>
+      <xdr:rowOff>82850</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -543,8 +534,8 @@
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+        <xdr:cNvPicPr preferRelativeResize="0">
+          <a:picLocks/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -562,7 +553,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="196850" y="101600"/>
-          <a:ext cx="3257550" cy="651387"/>
+          <a:ext cx="3042000" cy="648000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -669,10 +660,10 @@
       <xdr:rowOff>6350</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>6350</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>267050</xdr:colOff>
       <xdr:row>57</xdr:row>
-      <xdr:rowOff>86237</xdr:rowOff>
+      <xdr:rowOff>82850</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -683,8 +674,8 @@
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
+        <xdr:cNvPicPr preferRelativeResize="0">
+          <a:picLocks/>
         </xdr:cNvPicPr>
       </xdr:nvPicPr>
       <xdr:blipFill>
@@ -701,8 +692,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="196850" y="9385300"/>
-          <a:ext cx="3257550" cy="651387"/>
+          <a:off x="196850" y="9436100"/>
+          <a:ext cx="3042000" cy="648000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1223,1004 +1214,980 @@
     <col min="9" max="9" width="10.5703125" customWidth="1"/>
     <col min="10" max="10" width="12.5703125" customWidth="1"/>
     <col min="11" max="11" width="2.85546875" customWidth="1"/>
-    <col min="12" max="12" width="9.140625" hidden="1"/>
+    <col min="12" max="12" width="9.140625" hidden="1" customWidth="1"/>
+    <col min="13" max="24" width="0" hidden="1" customWidth="1"/>
     <col min="25" max="16384" width="9.140625" hidden="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="12" t="s">
+      <c r="B6" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="12"/>
-      <c r="D6" s="12"/>
-      <c r="E6" s="12"/>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12"/>
-      <c r="H6" s="12"/>
-      <c r="I6" s="12"/>
-      <c r="J6" s="12"/>
+      <c r="C6" s="27"/>
+      <c r="D6" s="27"/>
+      <c r="E6" s="27"/>
+      <c r="F6" s="27"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
     </row>
     <row r="7" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="1" t="s">
+      <c r="B8" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="3"/>
+      <c r="C8" s="19"/>
+      <c r="D8" s="19"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="19"/>
+      <c r="G8" s="19"/>
+      <c r="H8" s="19"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="20"/>
     </row>
     <row r="9" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="5"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="5"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="6"/>
+      <c r="B9" s="21"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="23"/>
     </row>
     <row r="10" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="7"/>
-      <c r="C10" s="8"/>
-      <c r="D10" s="8"/>
-      <c r="E10" s="8"/>
-      <c r="F10" s="8"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="9"/>
+      <c r="B10" s="24"/>
+      <c r="C10" s="25"/>
+      <c r="D10" s="25"/>
+      <c r="E10" s="25"/>
+      <c r="F10" s="25"/>
+      <c r="G10" s="25"/>
+      <c r="H10" s="25"/>
+      <c r="I10" s="25"/>
+      <c r="J10" s="26"/>
     </row>
     <row r="11" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="10" t="s">
+      <c r="B12" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="10"/>
-      <c r="D12" s="10"/>
-      <c r="E12" s="10"/>
-      <c r="F12" s="10"/>
-      <c r="G12" s="10"/>
-      <c r="H12" s="10"/>
-      <c r="I12" s="10"/>
-      <c r="J12" s="10"/>
-    </row>
-    <row r="13" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B13" s="11"/>
-      <c r="C13" s="11"/>
-      <c r="D13" s="11"/>
-      <c r="E13" s="11"/>
-    </row>
+      <c r="C12" s="17"/>
+      <c r="D12" s="17"/>
+      <c r="E12" s="17"/>
+      <c r="F12" s="17"/>
+      <c r="G12" s="17"/>
+      <c r="H12" s="17"/>
+      <c r="I12" s="17"/>
+      <c r="J12" s="17"/>
+    </row>
+    <row r="13" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="35" t="s">
+      <c r="B14" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="35"/>
-      <c r="D14" s="35"/>
-      <c r="E14" s="35"/>
-      <c r="F14" s="35" t="s">
+      <c r="C14" s="16"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="16"/>
+      <c r="F14" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="35" t="s">
+      <c r="G14" s="16"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="J14" s="35"/>
+      <c r="J14" s="16"/>
     </row>
     <row r="15" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B15" s="26"/>
-      <c r="C15" s="26"/>
-      <c r="D15" s="26"/>
-      <c r="E15" s="26"/>
-      <c r="F15" s="26"/>
-      <c r="G15" s="26"/>
-      <c r="H15" s="26"/>
-      <c r="I15" s="26"/>
-      <c r="J15" s="26"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
+      <c r="F15" s="2"/>
+      <c r="G15" s="2"/>
+      <c r="H15" s="2"/>
+      <c r="I15" s="2"/>
+      <c r="J15" s="2"/>
     </row>
     <row r="16" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="16"/>
-      <c r="C16" s="16"/>
-      <c r="D16" s="16"/>
-      <c r="E16" s="16"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="20"/>
-      <c r="J16" s="20"/>
+      <c r="B16" s="30"/>
+      <c r="C16" s="30"/>
+      <c r="D16" s="30"/>
+      <c r="E16" s="30"/>
+      <c r="F16" s="31"/>
+      <c r="G16" s="31"/>
+      <c r="H16" s="31"/>
+      <c r="I16" s="32"/>
+      <c r="J16" s="32"/>
     </row>
     <row r="17" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="17"/>
-      <c r="C17" s="17"/>
-      <c r="D17" s="17"/>
-      <c r="E17" s="17"/>
-      <c r="F17" s="21"/>
-      <c r="G17" s="21"/>
-      <c r="H17" s="21"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="12"/>
+      <c r="D17" s="12"/>
+      <c r="E17" s="12"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="33"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
     </row>
     <row r="18" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="17"/>
-      <c r="C18" s="17"/>
-      <c r="D18" s="17"/>
-      <c r="E18" s="17"/>
-      <c r="F18" s="21"/>
-      <c r="G18" s="21"/>
-      <c r="H18" s="21"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="12"/>
+      <c r="D18" s="12"/>
+      <c r="E18" s="12"/>
+      <c r="F18" s="33"/>
+      <c r="G18" s="33"/>
+      <c r="H18" s="33"/>
+      <c r="I18" s="34"/>
+      <c r="J18" s="34"/>
     </row>
     <row r="19" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="17"/>
-      <c r="C19" s="17"/>
-      <c r="D19" s="17"/>
-      <c r="E19" s="17"/>
-      <c r="F19" s="21"/>
-      <c r="G19" s="21"/>
-      <c r="H19" s="21"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="22"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="33"/>
+      <c r="G19" s="33"/>
+      <c r="H19" s="33"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="34"/>
     </row>
     <row r="20" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="18"/>
-      <c r="C20" s="18"/>
-      <c r="D20" s="18"/>
-      <c r="E20" s="18"/>
-      <c r="F20" s="21"/>
-      <c r="G20" s="21"/>
-      <c r="H20" s="21"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="22"/>
+      <c r="B20" s="11"/>
+      <c r="C20" s="11"/>
+      <c r="D20" s="11"/>
+      <c r="E20" s="11"/>
+      <c r="F20" s="33"/>
+      <c r="G20" s="33"/>
+      <c r="H20" s="33"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="34"/>
     </row>
     <row r="21" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="18"/>
-      <c r="C21" s="18"/>
-      <c r="D21" s="18"/>
-      <c r="E21" s="18"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="21"/>
-      <c r="H21" s="21"/>
-      <c r="I21" s="22"/>
-      <c r="J21" s="22"/>
+      <c r="B21" s="11"/>
+      <c r="C21" s="11"/>
+      <c r="D21" s="11"/>
+      <c r="E21" s="11"/>
+      <c r="F21" s="33"/>
+      <c r="G21" s="33"/>
+      <c r="H21" s="33"/>
+      <c r="I21" s="34"/>
+      <c r="J21" s="34"/>
     </row>
     <row r="22" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="19"/>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="23"/>
-      <c r="G22" s="23"/>
-      <c r="H22" s="23"/>
-      <c r="I22" s="24"/>
-      <c r="J22" s="24"/>
+      <c r="B22" s="7"/>
+      <c r="C22" s="7"/>
+      <c r="D22" s="7"/>
+      <c r="E22" s="7"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="36"/>
+      <c r="J22" s="36"/>
     </row>
     <row r="23" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B23" s="39"/>
-      <c r="C23" s="39"/>
-      <c r="D23" s="39"/>
-      <c r="E23" s="39"/>
-      <c r="F23" s="39"/>
-      <c r="G23" s="39"/>
-      <c r="H23" s="39"/>
-      <c r="I23" s="39"/>
-      <c r="J23" s="39"/>
+      <c r="B23" s="4"/>
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+      <c r="E23" s="4"/>
+      <c r="F23" s="4"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="4"/>
+      <c r="I23" s="4"/>
+      <c r="J23" s="4"/>
     </row>
     <row r="24" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="10" t="s">
+      <c r="B24" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="10"/>
-      <c r="D24" s="10"/>
-      <c r="E24" s="10"/>
-      <c r="F24" s="10"/>
-      <c r="G24" s="10"/>
-      <c r="H24" s="10"/>
-      <c r="I24" s="10"/>
-      <c r="J24" s="10"/>
+      <c r="C24" s="17"/>
+      <c r="D24" s="17"/>
+      <c r="E24" s="17"/>
+      <c r="F24" s="17"/>
+      <c r="G24" s="17"/>
+      <c r="H24" s="17"/>
+      <c r="I24" s="17"/>
+      <c r="J24" s="17"/>
     </row>
     <row r="25" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="35" t="s">
+      <c r="B26" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="35"/>
-      <c r="D26" s="35"/>
-      <c r="E26" s="35"/>
-      <c r="F26" s="35" t="s">
+      <c r="C26" s="16"/>
+      <c r="D26" s="16"/>
+      <c r="E26" s="16"/>
+      <c r="F26" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="35" t="s">
+      <c r="G26" s="16"/>
+      <c r="H26" s="16"/>
+      <c r="I26" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="J26" s="35"/>
+      <c r="J26" s="16"/>
     </row>
     <row r="27" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="27"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="34"/>
-      <c r="I28" s="30"/>
-      <c r="J28" s="31"/>
+      <c r="B28" s="13"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="15"/>
+      <c r="F28" s="37"/>
+      <c r="G28" s="38"/>
+      <c r="H28" s="39"/>
+      <c r="I28" s="40"/>
+      <c r="J28" s="41"/>
     </row>
     <row r="29" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="17"/>
-      <c r="C29" s="17"/>
-      <c r="D29" s="17"/>
-      <c r="E29" s="17"/>
-      <c r="F29" s="21"/>
-      <c r="G29" s="21"/>
-      <c r="H29" s="21"/>
-      <c r="I29" s="22"/>
-      <c r="J29" s="22"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="33"/>
+      <c r="G29" s="33"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="34"/>
+      <c r="J29" s="34"/>
     </row>
     <row r="30" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="17"/>
-      <c r="C30" s="17"/>
-      <c r="D30" s="17"/>
-      <c r="E30" s="17"/>
-      <c r="F30" s="21"/>
-      <c r="G30" s="21"/>
-      <c r="H30" s="21"/>
-      <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="33"/>
+      <c r="G30" s="33"/>
+      <c r="H30" s="33"/>
+      <c r="I30" s="34"/>
+      <c r="J30" s="34"/>
     </row>
     <row r="31" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="17"/>
-      <c r="C31" s="17"/>
-      <c r="D31" s="17"/>
-      <c r="E31" s="17"/>
-      <c r="F31" s="21"/>
-      <c r="G31" s="21"/>
-      <c r="H31" s="21"/>
-      <c r="I31" s="22"/>
-      <c r="J31" s="22"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="33"/>
+      <c r="G31" s="33"/>
+      <c r="H31" s="33"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="34"/>
     </row>
     <row r="32" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="18"/>
-      <c r="C32" s="18"/>
-      <c r="D32" s="18"/>
-      <c r="E32" s="18"/>
-      <c r="F32" s="21"/>
-      <c r="G32" s="21"/>
-      <c r="H32" s="21"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="22"/>
+      <c r="B32" s="11"/>
+      <c r="C32" s="11"/>
+      <c r="D32" s="11"/>
+      <c r="E32" s="11"/>
+      <c r="F32" s="33"/>
+      <c r="G32" s="33"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="34"/>
+      <c r="J32" s="34"/>
     </row>
     <row r="33" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="18"/>
-      <c r="C33" s="18"/>
-      <c r="D33" s="18"/>
-      <c r="E33" s="18"/>
-      <c r="F33" s="21"/>
-      <c r="G33" s="21"/>
-      <c r="H33" s="21"/>
-      <c r="I33" s="22"/>
-      <c r="J33" s="22"/>
+      <c r="B33" s="11"/>
+      <c r="C33" s="11"/>
+      <c r="D33" s="11"/>
+      <c r="E33" s="11"/>
+      <c r="F33" s="33"/>
+      <c r="G33" s="33"/>
+      <c r="H33" s="33"/>
+      <c r="I33" s="34"/>
+      <c r="J33" s="34"/>
     </row>
     <row r="34" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="19"/>
-      <c r="C34" s="19"/>
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="23"/>
-      <c r="G34" s="23"/>
-      <c r="H34" s="23"/>
-      <c r="I34" s="24"/>
-      <c r="J34" s="24"/>
+      <c r="B34" s="7"/>
+      <c r="C34" s="7"/>
+      <c r="D34" s="7"/>
+      <c r="E34" s="7"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="36"/>
+      <c r="J34" s="36"/>
     </row>
     <row r="35" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B35" s="39"/>
-      <c r="C35" s="39"/>
-      <c r="D35" s="39"/>
-      <c r="E35" s="39"/>
-      <c r="F35" s="39"/>
-      <c r="G35" s="39"/>
-      <c r="H35" s="39"/>
-      <c r="I35" s="39"/>
-      <c r="J35" s="39"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+      <c r="H35" s="4"/>
+      <c r="I35" s="4"/>
+      <c r="J35" s="4"/>
     </row>
     <row r="36" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="10" t="s">
+      <c r="B36" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C36" s="10"/>
-      <c r="D36" s="10"/>
-      <c r="E36" s="10"/>
-      <c r="F36" s="10"/>
-      <c r="G36" s="10"/>
-      <c r="H36" s="10"/>
-      <c r="I36" s="10"/>
-      <c r="J36" s="10"/>
+      <c r="C36" s="17"/>
+      <c r="D36" s="17"/>
+      <c r="E36" s="17"/>
+      <c r="F36" s="17"/>
+      <c r="G36" s="17"/>
+      <c r="H36" s="17"/>
+      <c r="I36" s="17"/>
+      <c r="J36" s="17"/>
     </row>
     <row r="37" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="35" t="s">
+      <c r="B38" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C38" s="35"/>
-      <c r="D38" s="35"/>
-      <c r="E38" s="35"/>
-      <c r="F38" s="35" t="s">
+      <c r="C38" s="16"/>
+      <c r="D38" s="16"/>
+      <c r="E38" s="16"/>
+      <c r="F38" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G38" s="35"/>
-      <c r="H38" s="35"/>
-      <c r="I38" s="35" t="s">
+      <c r="G38" s="16"/>
+      <c r="H38" s="16"/>
+      <c r="I38" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="J38" s="35"/>
+      <c r="J38" s="16"/>
     </row>
     <row r="39" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="27"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="29"/>
-      <c r="F40" s="32"/>
-      <c r="G40" s="33"/>
-      <c r="H40" s="34"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="31"/>
+      <c r="B40" s="13"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="15"/>
+      <c r="F40" s="37"/>
+      <c r="G40" s="38"/>
+      <c r="H40" s="39"/>
+      <c r="I40" s="40"/>
+      <c r="J40" s="41"/>
     </row>
     <row r="41" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17"/>
-      <c r="F41" s="21"/>
-      <c r="G41" s="21"/>
-      <c r="H41" s="21"/>
-      <c r="I41" s="22"/>
-      <c r="J41" s="22"/>
+      <c r="B41" s="12"/>
+      <c r="C41" s="12"/>
+      <c r="D41" s="12"/>
+      <c r="E41" s="12"/>
+      <c r="F41" s="33"/>
+      <c r="G41" s="33"/>
+      <c r="H41" s="33"/>
+      <c r="I41" s="34"/>
+      <c r="J41" s="34"/>
     </row>
     <row r="42" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="17"/>
-      <c r="C42" s="17"/>
-      <c r="D42" s="17"/>
-      <c r="E42" s="17"/>
-      <c r="F42" s="21"/>
-      <c r="G42" s="21"/>
-      <c r="H42" s="21"/>
-      <c r="I42" s="22"/>
-      <c r="J42" s="22"/>
+      <c r="B42" s="12"/>
+      <c r="C42" s="12"/>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12"/>
+      <c r="F42" s="33"/>
+      <c r="G42" s="33"/>
+      <c r="H42" s="33"/>
+      <c r="I42" s="34"/>
+      <c r="J42" s="34"/>
     </row>
     <row r="43" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="17"/>
-      <c r="C43" s="17"/>
-      <c r="D43" s="17"/>
-      <c r="E43" s="17"/>
-      <c r="F43" s="21"/>
-      <c r="G43" s="21"/>
-      <c r="H43" s="21"/>
-      <c r="I43" s="22"/>
-      <c r="J43" s="22"/>
+      <c r="B43" s="12"/>
+      <c r="C43" s="12"/>
+      <c r="D43" s="12"/>
+      <c r="E43" s="12"/>
+      <c r="F43" s="33"/>
+      <c r="G43" s="33"/>
+      <c r="H43" s="33"/>
+      <c r="I43" s="34"/>
+      <c r="J43" s="34"/>
     </row>
     <row r="44" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="18"/>
-      <c r="C44" s="18"/>
-      <c r="D44" s="18"/>
-      <c r="E44" s="18"/>
-      <c r="F44" s="21"/>
-      <c r="G44" s="21"/>
-      <c r="H44" s="21"/>
-      <c r="I44" s="22"/>
-      <c r="J44" s="22"/>
+      <c r="B44" s="11"/>
+      <c r="C44" s="11"/>
+      <c r="D44" s="11"/>
+      <c r="E44" s="11"/>
+      <c r="F44" s="33"/>
+      <c r="G44" s="33"/>
+      <c r="H44" s="33"/>
+      <c r="I44" s="34"/>
+      <c r="J44" s="34"/>
     </row>
     <row r="45" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="18"/>
-      <c r="C45" s="18"/>
-      <c r="D45" s="18"/>
-      <c r="E45" s="18"/>
-      <c r="F45" s="21"/>
-      <c r="G45" s="21"/>
-      <c r="H45" s="21"/>
-      <c r="I45" s="22"/>
-      <c r="J45" s="22"/>
+      <c r="B45" s="11"/>
+      <c r="C45" s="11"/>
+      <c r="D45" s="11"/>
+      <c r="E45" s="11"/>
+      <c r="F45" s="33"/>
+      <c r="G45" s="33"/>
+      <c r="H45" s="33"/>
+      <c r="I45" s="34"/>
+      <c r="J45" s="34"/>
     </row>
     <row r="46" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="19"/>
-      <c r="C46" s="19"/>
-      <c r="D46" s="19"/>
-      <c r="E46" s="19"/>
-      <c r="F46" s="23"/>
-      <c r="G46" s="23"/>
-      <c r="H46" s="23"/>
-      <c r="I46" s="24"/>
-      <c r="J46" s="24"/>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="35"/>
+      <c r="G46" s="35"/>
+      <c r="H46" s="35"/>
+      <c r="I46" s="36"/>
+      <c r="J46" s="36"/>
     </row>
     <row r="47" spans="2:10" ht="8.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="36"/>
-      <c r="C47" s="36"/>
-      <c r="D47" s="36"/>
-      <c r="E47" s="37"/>
-      <c r="F47" s="37"/>
-      <c r="G47" s="37"/>
-      <c r="H47" s="37"/>
-      <c r="I47" s="37"/>
-      <c r="J47" s="38"/>
+      <c r="B47" s="28"/>
+      <c r="C47" s="28"/>
+      <c r="D47" s="28"/>
+      <c r="E47" s="29"/>
+      <c r="F47" s="29"/>
+      <c r="G47" s="29"/>
+      <c r="H47" s="29"/>
+      <c r="I47" s="29"/>
+      <c r="J47" s="3"/>
     </row>
     <row r="48" spans="2:10" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="13"/>
-      <c r="C50" s="13"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="15"/>
-      <c r="G50" s="15"/>
-      <c r="H50" s="15"/>
-      <c r="I50" s="15"/>
-      <c r="J50" s="14"/>
+      <c r="B50" s="8"/>
+      <c r="C50" s="8"/>
+      <c r="D50" s="8"/>
+      <c r="E50" s="1"/>
+      <c r="F50" s="9"/>
+      <c r="G50" s="9"/>
+      <c r="H50" s="9"/>
+      <c r="I50" s="9"/>
+      <c r="J50" s="1"/>
     </row>
     <row r="51" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="40" t="s">
+      <c r="B51" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C51" s="40"/>
-      <c r="D51" s="40"/>
-      <c r="E51" s="40"/>
-      <c r="F51" s="40"/>
-      <c r="G51" s="40"/>
-      <c r="H51" s="40"/>
-      <c r="I51" s="40"/>
-      <c r="J51" s="40"/>
+      <c r="C51" s="10"/>
+      <c r="D51" s="10"/>
+      <c r="E51" s="10"/>
+      <c r="F51" s="10"/>
+      <c r="G51" s="10"/>
+      <c r="H51" s="10"/>
+      <c r="I51" s="10"/>
+      <c r="J51" s="10"/>
     </row>
     <row r="52" spans="2:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="41" t="s">
+      <c r="B52" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C52" s="41"/>
-      <c r="D52" s="41"/>
-      <c r="E52" s="41"/>
-      <c r="F52" s="41"/>
-      <c r="G52" s="41"/>
-      <c r="H52" s="41"/>
-      <c r="I52" s="41"/>
-      <c r="J52" s="41"/>
+      <c r="C52" s="5"/>
+      <c r="D52" s="5"/>
+      <c r="E52" s="5"/>
+      <c r="F52" s="5"/>
+      <c r="G52" s="5"/>
+      <c r="H52" s="5"/>
+      <c r="I52" s="5"/>
+      <c r="J52" s="5"/>
     </row>
     <row r="53" spans="2:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="42" t="s">
+      <c r="B53" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C53" s="42"/>
-      <c r="D53" s="42"/>
-      <c r="E53" s="42"/>
-      <c r="F53" s="42"/>
-      <c r="G53" s="42"/>
-      <c r="H53" s="42"/>
-      <c r="I53" s="42"/>
-      <c r="J53" s="42"/>
+      <c r="C53" s="6"/>
+      <c r="D53" s="6"/>
+      <c r="E53" s="6"/>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6"/>
+      <c r="H53" s="6"/>
+      <c r="I53" s="6"/>
+      <c r="J53" s="6"/>
     </row>
     <row r="54" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="59" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="12" t="s">
+      <c r="B59" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C59" s="12"/>
-      <c r="D59" s="12"/>
-      <c r="E59" s="12"/>
-      <c r="F59" s="12"/>
-      <c r="G59" s="12"/>
-      <c r="H59" s="12"/>
-      <c r="I59" s="12"/>
-      <c r="J59" s="12"/>
+      <c r="C59" s="27"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="27"/>
+      <c r="F59" s="27"/>
+      <c r="G59" s="27"/>
+      <c r="H59" s="27"/>
+      <c r="I59" s="27"/>
+      <c r="J59" s="27"/>
     </row>
     <row r="60" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="61" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="1" t="s">
+      <c r="B61" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C61" s="2"/>
-      <c r="D61" s="2"/>
-      <c r="E61" s="2"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="H61" s="2"/>
-      <c r="I61" s="2"/>
-      <c r="J61" s="3"/>
+      <c r="C61" s="19"/>
+      <c r="D61" s="19"/>
+      <c r="E61" s="19"/>
+      <c r="F61" s="19"/>
+      <c r="G61" s="19"/>
+      <c r="H61" s="19"/>
+      <c r="I61" s="19"/>
+      <c r="J61" s="20"/>
     </row>
     <row r="62" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="4"/>
-      <c r="C62" s="5"/>
-      <c r="D62" s="5"/>
-      <c r="E62" s="5"/>
-      <c r="F62" s="5"/>
-      <c r="G62" s="5"/>
-      <c r="H62" s="5"/>
-      <c r="I62" s="5"/>
-      <c r="J62" s="6"/>
+      <c r="B62" s="21"/>
+      <c r="C62" s="22"/>
+      <c r="D62" s="22"/>
+      <c r="E62" s="22"/>
+      <c r="F62" s="22"/>
+      <c r="G62" s="22"/>
+      <c r="H62" s="22"/>
+      <c r="I62" s="22"/>
+      <c r="J62" s="23"/>
     </row>
     <row r="63" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="7"/>
-      <c r="C63" s="8"/>
-      <c r="D63" s="8"/>
-      <c r="E63" s="8"/>
-      <c r="F63" s="8"/>
-      <c r="G63" s="8"/>
-      <c r="H63" s="8"/>
-      <c r="I63" s="8"/>
-      <c r="J63" s="9"/>
+      <c r="B63" s="24"/>
+      <c r="C63" s="25"/>
+      <c r="D63" s="25"/>
+      <c r="E63" s="25"/>
+      <c r="F63" s="25"/>
+      <c r="G63" s="25"/>
+      <c r="H63" s="25"/>
+      <c r="I63" s="25"/>
+      <c r="J63" s="26"/>
     </row>
     <row r="64" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="65" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="10" t="s">
+      <c r="B65" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="10"/>
-      <c r="D65" s="10"/>
-      <c r="E65" s="10"/>
-      <c r="F65" s="10"/>
-      <c r="G65" s="10"/>
-      <c r="H65" s="10"/>
-      <c r="I65" s="10"/>
-      <c r="J65" s="10"/>
+      <c r="C65" s="17"/>
+      <c r="D65" s="17"/>
+      <c r="E65" s="17"/>
+      <c r="F65" s="17"/>
+      <c r="G65" s="17"/>
+      <c r="H65" s="17"/>
+      <c r="I65" s="17"/>
+      <c r="J65" s="17"/>
     </row>
     <row r="66" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B67" s="35" t="s">
+      <c r="B67" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="35"/>
-      <c r="D67" s="35"/>
-      <c r="E67" s="35"/>
-      <c r="F67" s="35" t="s">
+      <c r="C67" s="16"/>
+      <c r="D67" s="16"/>
+      <c r="E67" s="16"/>
+      <c r="F67" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G67" s="35"/>
-      <c r="H67" s="35"/>
-      <c r="I67" s="35" t="s">
+      <c r="G67" s="16"/>
+      <c r="H67" s="16"/>
+      <c r="I67" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="J67" s="35"/>
+      <c r="J67" s="16"/>
     </row>
     <row r="68" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="69" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="27"/>
-      <c r="C69" s="28"/>
-      <c r="D69" s="28"/>
-      <c r="E69" s="29"/>
-      <c r="F69" s="32"/>
-      <c r="G69" s="33"/>
-      <c r="H69" s="34"/>
-      <c r="I69" s="30"/>
-      <c r="J69" s="31"/>
+      <c r="B69" s="13"/>
+      <c r="C69" s="14"/>
+      <c r="D69" s="14"/>
+      <c r="E69" s="15"/>
+      <c r="F69" s="37"/>
+      <c r="G69" s="38"/>
+      <c r="H69" s="39"/>
+      <c r="I69" s="40"/>
+      <c r="J69" s="41"/>
     </row>
     <row r="70" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="17"/>
-      <c r="C70" s="17"/>
-      <c r="D70" s="17"/>
-      <c r="E70" s="17"/>
-      <c r="F70" s="21"/>
-      <c r="G70" s="21"/>
-      <c r="H70" s="21"/>
-      <c r="I70" s="22"/>
-      <c r="J70" s="22"/>
+      <c r="B70" s="12"/>
+      <c r="C70" s="12"/>
+      <c r="D70" s="12"/>
+      <c r="E70" s="12"/>
+      <c r="F70" s="33"/>
+      <c r="G70" s="33"/>
+      <c r="H70" s="33"/>
+      <c r="I70" s="34"/>
+      <c r="J70" s="34"/>
     </row>
     <row r="71" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="17"/>
-      <c r="C71" s="17"/>
-      <c r="D71" s="17"/>
-      <c r="E71" s="17"/>
-      <c r="F71" s="21"/>
-      <c r="G71" s="21"/>
-      <c r="H71" s="21"/>
-      <c r="I71" s="22"/>
-      <c r="J71" s="22"/>
+      <c r="B71" s="12"/>
+      <c r="C71" s="12"/>
+      <c r="D71" s="12"/>
+      <c r="E71" s="12"/>
+      <c r="F71" s="33"/>
+      <c r="G71" s="33"/>
+      <c r="H71" s="33"/>
+      <c r="I71" s="34"/>
+      <c r="J71" s="34"/>
     </row>
     <row r="72" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="17"/>
-      <c r="C72" s="17"/>
-      <c r="D72" s="17"/>
-      <c r="E72" s="17"/>
-      <c r="F72" s="21"/>
-      <c r="G72" s="21"/>
-      <c r="H72" s="21"/>
-      <c r="I72" s="22"/>
-      <c r="J72" s="22"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="12"/>
+      <c r="D72" s="12"/>
+      <c r="E72" s="12"/>
+      <c r="F72" s="33"/>
+      <c r="G72" s="33"/>
+      <c r="H72" s="33"/>
+      <c r="I72" s="34"/>
+      <c r="J72" s="34"/>
     </row>
     <row r="73" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="18"/>
-      <c r="C73" s="18"/>
-      <c r="D73" s="18"/>
-      <c r="E73" s="18"/>
-      <c r="F73" s="21"/>
-      <c r="G73" s="21"/>
-      <c r="H73" s="21"/>
-      <c r="I73" s="22"/>
-      <c r="J73" s="22"/>
+      <c r="B73" s="11"/>
+      <c r="C73" s="11"/>
+      <c r="D73" s="11"/>
+      <c r="E73" s="11"/>
+      <c r="F73" s="33"/>
+      <c r="G73" s="33"/>
+      <c r="H73" s="33"/>
+      <c r="I73" s="34"/>
+      <c r="J73" s="34"/>
     </row>
     <row r="74" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="18"/>
-      <c r="C74" s="18"/>
-      <c r="D74" s="18"/>
-      <c r="E74" s="18"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="21"/>
-      <c r="H74" s="21"/>
-      <c r="I74" s="22"/>
-      <c r="J74" s="22"/>
+      <c r="B74" s="11"/>
+      <c r="C74" s="11"/>
+      <c r="D74" s="11"/>
+      <c r="E74" s="11"/>
+      <c r="F74" s="33"/>
+      <c r="G74" s="33"/>
+      <c r="H74" s="33"/>
+      <c r="I74" s="34"/>
+      <c r="J74" s="34"/>
     </row>
     <row r="75" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="19"/>
-      <c r="C75" s="19"/>
-      <c r="D75" s="19"/>
-      <c r="E75" s="19"/>
-      <c r="F75" s="23"/>
-      <c r="G75" s="23"/>
-      <c r="H75" s="23"/>
-      <c r="I75" s="24"/>
-      <c r="J75" s="24"/>
+      <c r="B75" s="7"/>
+      <c r="C75" s="7"/>
+      <c r="D75" s="7"/>
+      <c r="E75" s="7"/>
+      <c r="F75" s="35"/>
+      <c r="G75" s="35"/>
+      <c r="H75" s="35"/>
+      <c r="I75" s="36"/>
+      <c r="J75" s="36"/>
     </row>
     <row r="76" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="10" t="s">
+      <c r="B77" s="17" t="s">
         <v>2</v>
       </c>
-      <c r="C77" s="10"/>
-      <c r="D77" s="10"/>
-      <c r="E77" s="10"/>
-      <c r="F77" s="10"/>
-      <c r="G77" s="10"/>
-      <c r="H77" s="10"/>
-      <c r="I77" s="10"/>
-      <c r="J77" s="10"/>
+      <c r="C77" s="17"/>
+      <c r="D77" s="17"/>
+      <c r="E77" s="17"/>
+      <c r="F77" s="17"/>
+      <c r="G77" s="17"/>
+      <c r="H77" s="17"/>
+      <c r="I77" s="17"/>
+      <c r="J77" s="17"/>
     </row>
     <row r="78" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="79" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B79" s="35" t="s">
+      <c r="B79" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C79" s="35"/>
-      <c r="D79" s="35"/>
-      <c r="E79" s="35"/>
-      <c r="F79" s="35" t="s">
+      <c r="C79" s="16"/>
+      <c r="D79" s="16"/>
+      <c r="E79" s="16"/>
+      <c r="F79" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G79" s="35"/>
-      <c r="H79" s="35"/>
-      <c r="I79" s="35" t="s">
+      <c r="G79" s="16"/>
+      <c r="H79" s="16"/>
+      <c r="I79" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="J79" s="35"/>
+      <c r="J79" s="16"/>
     </row>
     <row r="80" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="81" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="27"/>
-      <c r="C81" s="28"/>
-      <c r="D81" s="28"/>
-      <c r="E81" s="29"/>
-      <c r="F81" s="32"/>
-      <c r="G81" s="33"/>
-      <c r="H81" s="34"/>
-      <c r="I81" s="30"/>
-      <c r="J81" s="31"/>
+      <c r="B81" s="13"/>
+      <c r="C81" s="14"/>
+      <c r="D81" s="14"/>
+      <c r="E81" s="15"/>
+      <c r="F81" s="37"/>
+      <c r="G81" s="38"/>
+      <c r="H81" s="39"/>
+      <c r="I81" s="40"/>
+      <c r="J81" s="41"/>
     </row>
     <row r="82" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="17"/>
-      <c r="C82" s="17"/>
-      <c r="D82" s="17"/>
-      <c r="E82" s="17"/>
-      <c r="F82" s="21"/>
-      <c r="G82" s="21"/>
-      <c r="H82" s="21"/>
-      <c r="I82" s="22"/>
-      <c r="J82" s="22"/>
+      <c r="B82" s="12"/>
+      <c r="C82" s="12"/>
+      <c r="D82" s="12"/>
+      <c r="E82" s="12"/>
+      <c r="F82" s="33"/>
+      <c r="G82" s="33"/>
+      <c r="H82" s="33"/>
+      <c r="I82" s="34"/>
+      <c r="J82" s="34"/>
     </row>
     <row r="83" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="17"/>
-      <c r="C83" s="17"/>
-      <c r="D83" s="17"/>
-      <c r="E83" s="17"/>
-      <c r="F83" s="21"/>
-      <c r="G83" s="21"/>
-      <c r="H83" s="21"/>
-      <c r="I83" s="22"/>
-      <c r="J83" s="22"/>
+      <c r="B83" s="12"/>
+      <c r="C83" s="12"/>
+      <c r="D83" s="12"/>
+      <c r="E83" s="12"/>
+      <c r="F83" s="33"/>
+      <c r="G83" s="33"/>
+      <c r="H83" s="33"/>
+      <c r="I83" s="34"/>
+      <c r="J83" s="34"/>
     </row>
     <row r="84" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="17"/>
-      <c r="C84" s="17"/>
-      <c r="D84" s="17"/>
-      <c r="E84" s="17"/>
-      <c r="F84" s="21"/>
-      <c r="G84" s="21"/>
-      <c r="H84" s="21"/>
-      <c r="I84" s="22"/>
-      <c r="J84" s="22"/>
+      <c r="B84" s="12"/>
+      <c r="C84" s="12"/>
+      <c r="D84" s="12"/>
+      <c r="E84" s="12"/>
+      <c r="F84" s="33"/>
+      <c r="G84" s="33"/>
+      <c r="H84" s="33"/>
+      <c r="I84" s="34"/>
+      <c r="J84" s="34"/>
     </row>
     <row r="85" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="18"/>
-      <c r="C85" s="18"/>
-      <c r="D85" s="18"/>
-      <c r="E85" s="18"/>
-      <c r="F85" s="21"/>
-      <c r="G85" s="21"/>
-      <c r="H85" s="21"/>
-      <c r="I85" s="22"/>
-      <c r="J85" s="22"/>
+      <c r="B85" s="11"/>
+      <c r="C85" s="11"/>
+      <c r="D85" s="11"/>
+      <c r="E85" s="11"/>
+      <c r="F85" s="33"/>
+      <c r="G85" s="33"/>
+      <c r="H85" s="33"/>
+      <c r="I85" s="34"/>
+      <c r="J85" s="34"/>
     </row>
     <row r="86" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="18"/>
-      <c r="C86" s="18"/>
-      <c r="D86" s="18"/>
-      <c r="E86" s="18"/>
-      <c r="F86" s="21"/>
-      <c r="G86" s="21"/>
-      <c r="H86" s="21"/>
-      <c r="I86" s="22"/>
-      <c r="J86" s="22"/>
+      <c r="B86" s="11"/>
+      <c r="C86" s="11"/>
+      <c r="D86" s="11"/>
+      <c r="E86" s="11"/>
+      <c r="F86" s="33"/>
+      <c r="G86" s="33"/>
+      <c r="H86" s="33"/>
+      <c r="I86" s="34"/>
+      <c r="J86" s="34"/>
     </row>
     <row r="87" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="19"/>
-      <c r="C87" s="19"/>
-      <c r="D87" s="19"/>
-      <c r="E87" s="19"/>
-      <c r="F87" s="23"/>
-      <c r="G87" s="23"/>
-      <c r="H87" s="23"/>
-      <c r="I87" s="24"/>
-      <c r="J87" s="24"/>
+      <c r="B87" s="7"/>
+      <c r="C87" s="7"/>
+      <c r="D87" s="7"/>
+      <c r="E87" s="7"/>
+      <c r="F87" s="35"/>
+      <c r="G87" s="35"/>
+      <c r="H87" s="35"/>
+      <c r="I87" s="36"/>
+      <c r="J87" s="36"/>
     </row>
     <row r="88" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="89" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="10" t="s">
+      <c r="B89" s="17" t="s">
         <v>3</v>
       </c>
-      <c r="C89" s="10"/>
-      <c r="D89" s="10"/>
-      <c r="E89" s="10"/>
-      <c r="F89" s="10"/>
-      <c r="G89" s="10"/>
-      <c r="H89" s="10"/>
-      <c r="I89" s="10"/>
-      <c r="J89" s="10"/>
+      <c r="C89" s="17"/>
+      <c r="D89" s="17"/>
+      <c r="E89" s="17"/>
+      <c r="F89" s="17"/>
+      <c r="G89" s="17"/>
+      <c r="H89" s="17"/>
+      <c r="I89" s="17"/>
+      <c r="J89" s="17"/>
     </row>
     <row r="90" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="91" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B91" s="35" t="s">
+      <c r="B91" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="35"/>
-      <c r="D91" s="35"/>
-      <c r="E91" s="35"/>
-      <c r="F91" s="35" t="s">
+      <c r="C91" s="16"/>
+      <c r="D91" s="16"/>
+      <c r="E91" s="16"/>
+      <c r="F91" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="G91" s="35"/>
-      <c r="H91" s="35"/>
-      <c r="I91" s="35" t="s">
+      <c r="G91" s="16"/>
+      <c r="H91" s="16"/>
+      <c r="I91" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="J91" s="35"/>
+      <c r="J91" s="16"/>
     </row>
     <row r="92" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="93" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="27"/>
-      <c r="C93" s="28"/>
-      <c r="D93" s="28"/>
-      <c r="E93" s="29"/>
-      <c r="F93" s="32"/>
-      <c r="G93" s="33"/>
-      <c r="H93" s="34"/>
-      <c r="I93" s="30"/>
-      <c r="J93" s="31"/>
+      <c r="B93" s="13"/>
+      <c r="C93" s="14"/>
+      <c r="D93" s="14"/>
+      <c r="E93" s="15"/>
+      <c r="F93" s="37"/>
+      <c r="G93" s="38"/>
+      <c r="H93" s="39"/>
+      <c r="I93" s="40"/>
+      <c r="J93" s="41"/>
     </row>
     <row r="94" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B94" s="17"/>
-      <c r="C94" s="17"/>
-      <c r="D94" s="17"/>
-      <c r="E94" s="17"/>
-      <c r="F94" s="21"/>
-      <c r="G94" s="21"/>
-      <c r="H94" s="21"/>
-      <c r="I94" s="22"/>
-      <c r="J94" s="22"/>
+      <c r="B94" s="12"/>
+      <c r="C94" s="12"/>
+      <c r="D94" s="12"/>
+      <c r="E94" s="12"/>
+      <c r="F94" s="33"/>
+      <c r="G94" s="33"/>
+      <c r="H94" s="33"/>
+      <c r="I94" s="34"/>
+      <c r="J94" s="34"/>
     </row>
     <row r="95" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="17"/>
-      <c r="C95" s="17"/>
-      <c r="D95" s="17"/>
-      <c r="E95" s="17"/>
-      <c r="F95" s="21"/>
-      <c r="G95" s="21"/>
-      <c r="H95" s="21"/>
-      <c r="I95" s="22"/>
-      <c r="J95" s="22"/>
+      <c r="B95" s="12"/>
+      <c r="C95" s="12"/>
+      <c r="D95" s="12"/>
+      <c r="E95" s="12"/>
+      <c r="F95" s="33"/>
+      <c r="G95" s="33"/>
+      <c r="H95" s="33"/>
+      <c r="I95" s="34"/>
+      <c r="J95" s="34"/>
     </row>
     <row r="96" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B96" s="17"/>
-      <c r="C96" s="17"/>
-      <c r="D96" s="17"/>
-      <c r="E96" s="17"/>
-      <c r="F96" s="21"/>
-      <c r="G96" s="21"/>
-      <c r="H96" s="21"/>
-      <c r="I96" s="22"/>
-      <c r="J96" s="22"/>
+      <c r="B96" s="12"/>
+      <c r="C96" s="12"/>
+      <c r="D96" s="12"/>
+      <c r="E96" s="12"/>
+      <c r="F96" s="33"/>
+      <c r="G96" s="33"/>
+      <c r="H96" s="33"/>
+      <c r="I96" s="34"/>
+      <c r="J96" s="34"/>
     </row>
     <row r="97" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B97" s="18"/>
-      <c r="C97" s="18"/>
-      <c r="D97" s="18"/>
-      <c r="E97" s="18"/>
-      <c r="F97" s="21"/>
-      <c r="G97" s="21"/>
-      <c r="H97" s="21"/>
-      <c r="I97" s="22"/>
-      <c r="J97" s="22"/>
+      <c r="B97" s="11"/>
+      <c r="C97" s="11"/>
+      <c r="D97" s="11"/>
+      <c r="E97" s="11"/>
+      <c r="F97" s="33"/>
+      <c r="G97" s="33"/>
+      <c r="H97" s="33"/>
+      <c r="I97" s="34"/>
+      <c r="J97" s="34"/>
     </row>
     <row r="98" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B98" s="18"/>
-      <c r="C98" s="18"/>
-      <c r="D98" s="18"/>
-      <c r="E98" s="18"/>
-      <c r="F98" s="21"/>
-      <c r="G98" s="21"/>
-      <c r="H98" s="21"/>
-      <c r="I98" s="22"/>
-      <c r="J98" s="22"/>
+      <c r="B98" s="11"/>
+      <c r="C98" s="11"/>
+      <c r="D98" s="11"/>
+      <c r="E98" s="11"/>
+      <c r="F98" s="33"/>
+      <c r="G98" s="33"/>
+      <c r="H98" s="33"/>
+      <c r="I98" s="34"/>
+      <c r="J98" s="34"/>
     </row>
     <row r="99" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B99" s="19"/>
-      <c r="C99" s="19"/>
-      <c r="D99" s="19"/>
-      <c r="E99" s="19"/>
-      <c r="F99" s="23"/>
-      <c r="G99" s="23"/>
-      <c r="H99" s="23"/>
-      <c r="I99" s="24"/>
-      <c r="J99" s="24"/>
+      <c r="B99" s="7"/>
+      <c r="C99" s="7"/>
+      <c r="D99" s="7"/>
+      <c r="E99" s="7"/>
+      <c r="F99" s="35"/>
+      <c r="G99" s="35"/>
+      <c r="H99" s="35"/>
+      <c r="I99" s="36"/>
+      <c r="J99" s="36"/>
     </row>
     <row r="100" spans="2:10" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="101" spans="2:10" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="102" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="103" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="13"/>
-      <c r="C103" s="13"/>
-      <c r="D103" s="13"/>
-      <c r="E103" s="14"/>
-      <c r="F103" s="15"/>
-      <c r="G103" s="15"/>
-      <c r="H103" s="15"/>
-      <c r="I103" s="15"/>
-      <c r="J103" s="14"/>
+      <c r="B103" s="8"/>
+      <c r="C103" s="8"/>
+      <c r="D103" s="8"/>
+      <c r="E103" s="1"/>
+      <c r="F103" s="9"/>
+      <c r="G103" s="9"/>
+      <c r="H103" s="9"/>
+      <c r="I103" s="9"/>
+      <c r="J103" s="1"/>
     </row>
     <row r="104" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B104" s="40" t="s">
+      <c r="B104" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="C104" s="40"/>
-      <c r="D104" s="40"/>
-      <c r="E104" s="40"/>
-      <c r="F104" s="40"/>
-      <c r="G104" s="40"/>
-      <c r="H104" s="40"/>
-      <c r="I104" s="40"/>
-      <c r="J104" s="40"/>
+      <c r="C104" s="10"/>
+      <c r="D104" s="10"/>
+      <c r="E104" s="10"/>
+      <c r="F104" s="10"/>
+      <c r="G104" s="10"/>
+      <c r="H104" s="10"/>
+      <c r="I104" s="10"/>
+      <c r="J104" s="10"/>
     </row>
     <row r="105" spans="2:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B105" s="41" t="s">
+      <c r="B105" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C105" s="41"/>
-      <c r="D105" s="41"/>
-      <c r="E105" s="41"/>
-      <c r="F105" s="41"/>
-      <c r="G105" s="41"/>
-      <c r="H105" s="41"/>
-      <c r="I105" s="41"/>
-      <c r="J105" s="41"/>
+      <c r="C105" s="5"/>
+      <c r="D105" s="5"/>
+      <c r="E105" s="5"/>
+      <c r="F105" s="5"/>
+      <c r="G105" s="5"/>
+      <c r="H105" s="5"/>
+      <c r="I105" s="5"/>
+      <c r="J105" s="5"/>
     </row>
     <row r="106" spans="2:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="42" t="s">
+      <c r="B106" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="C106" s="42"/>
-      <c r="D106" s="42"/>
-      <c r="E106" s="42"/>
-      <c r="F106" s="42"/>
-      <c r="G106" s="42"/>
-      <c r="H106" s="42"/>
-      <c r="I106" s="42"/>
-      <c r="J106" s="42"/>
+      <c r="C106" s="6"/>
+      <c r="D106" s="6"/>
+      <c r="E106" s="6"/>
+      <c r="F106" s="6"/>
+      <c r="G106" s="6"/>
+      <c r="H106" s="6"/>
+      <c r="I106" s="6"/>
+      <c r="J106" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="166">
-    <mergeCell ref="B105:J105"/>
-    <mergeCell ref="B106:J106"/>
-    <mergeCell ref="B99:E99"/>
-    <mergeCell ref="F99:H99"/>
-    <mergeCell ref="I99:J99"/>
-    <mergeCell ref="B103:D103"/>
-    <mergeCell ref="F103:I103"/>
-    <mergeCell ref="B104:J104"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="F97:H97"/>
-    <mergeCell ref="I97:J97"/>
-    <mergeCell ref="B98:E98"/>
-    <mergeCell ref="F98:H98"/>
-    <mergeCell ref="I98:J98"/>
-    <mergeCell ref="B95:E95"/>
-    <mergeCell ref="F95:H95"/>
-    <mergeCell ref="I95:J95"/>
-    <mergeCell ref="B96:E96"/>
-    <mergeCell ref="F96:H96"/>
-    <mergeCell ref="I96:J96"/>
-    <mergeCell ref="B93:E93"/>
-    <mergeCell ref="F93:H93"/>
-    <mergeCell ref="I93:J93"/>
-    <mergeCell ref="B94:E94"/>
-    <mergeCell ref="F94:H94"/>
-    <mergeCell ref="I94:J94"/>
-    <mergeCell ref="B86:E86"/>
-    <mergeCell ref="F86:H86"/>
-    <mergeCell ref="I86:J86"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="F87:H87"/>
-    <mergeCell ref="I87:J87"/>
-    <mergeCell ref="B84:E84"/>
-    <mergeCell ref="F84:H84"/>
-    <mergeCell ref="I84:J84"/>
-    <mergeCell ref="B85:E85"/>
-    <mergeCell ref="F85:H85"/>
-    <mergeCell ref="I85:J85"/>
-    <mergeCell ref="B82:E82"/>
-    <mergeCell ref="F82:H82"/>
-    <mergeCell ref="I82:J82"/>
-    <mergeCell ref="B83:E83"/>
-    <mergeCell ref="F83:H83"/>
-    <mergeCell ref="I83:J83"/>
-    <mergeCell ref="B74:E74"/>
-    <mergeCell ref="F74:H74"/>
-    <mergeCell ref="I74:J74"/>
-    <mergeCell ref="B75:E75"/>
-    <mergeCell ref="F75:H75"/>
-    <mergeCell ref="I75:J75"/>
-    <mergeCell ref="B72:E72"/>
-    <mergeCell ref="F72:H72"/>
-    <mergeCell ref="I72:J72"/>
-    <mergeCell ref="B73:E73"/>
-    <mergeCell ref="F73:H73"/>
-    <mergeCell ref="I73:J73"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="F70:H70"/>
-    <mergeCell ref="I70:J70"/>
-    <mergeCell ref="B71:E71"/>
-    <mergeCell ref="F71:H71"/>
-    <mergeCell ref="I71:J71"/>
-    <mergeCell ref="B79:E79"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="I79:J79"/>
-    <mergeCell ref="B89:J89"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="F91:H91"/>
-    <mergeCell ref="I91:J91"/>
-    <mergeCell ref="B81:E81"/>
-    <mergeCell ref="F81:H81"/>
-    <mergeCell ref="I81:J81"/>
-    <mergeCell ref="B61:J63"/>
-    <mergeCell ref="B65:J65"/>
-    <mergeCell ref="B77:J77"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="F67:H67"/>
-    <mergeCell ref="I67:J67"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="F69:H69"/>
-    <mergeCell ref="I69:J69"/>
+    <mergeCell ref="B6:J6"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="B26:E26"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="B24:J24"/>
+    <mergeCell ref="B20:E20"/>
+    <mergeCell ref="B21:E21"/>
+    <mergeCell ref="B22:E22"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B19:E19"/>
+    <mergeCell ref="B8:J10"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B36:J36"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="F43:H43"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I31:J31"/>
     <mergeCell ref="B50:D50"/>
     <mergeCell ref="F50:I50"/>
     <mergeCell ref="B51:J51"/>
@@ -2245,67 +2212,87 @@
     <mergeCell ref="I44:J44"/>
     <mergeCell ref="I45:J45"/>
     <mergeCell ref="I33:J33"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="B6:J6"/>
-    <mergeCell ref="B28:E28"/>
-    <mergeCell ref="B29:E29"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B31:E31"/>
-    <mergeCell ref="B32:E32"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B26:E26"/>
-    <mergeCell ref="B36:J36"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="B24:J24"/>
-    <mergeCell ref="B20:E20"/>
-    <mergeCell ref="B21:E21"/>
-    <mergeCell ref="B22:E22"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B19:E19"/>
-    <mergeCell ref="B8:J10"/>
-    <mergeCell ref="B12:J12"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="B16:E16"/>
+    <mergeCell ref="B89:J89"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="F91:H91"/>
+    <mergeCell ref="I91:J91"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="F81:H81"/>
+    <mergeCell ref="I81:J81"/>
+    <mergeCell ref="B61:J63"/>
+    <mergeCell ref="B65:J65"/>
+    <mergeCell ref="B77:J77"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="F67:H67"/>
+    <mergeCell ref="I67:J67"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="F69:H69"/>
+    <mergeCell ref="I69:J69"/>
+    <mergeCell ref="B72:E72"/>
+    <mergeCell ref="F72:H72"/>
+    <mergeCell ref="I72:J72"/>
+    <mergeCell ref="B73:E73"/>
+    <mergeCell ref="F73:H73"/>
+    <mergeCell ref="I73:J73"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="F70:H70"/>
+    <mergeCell ref="I70:J70"/>
+    <mergeCell ref="B71:E71"/>
+    <mergeCell ref="F71:H71"/>
+    <mergeCell ref="I71:J71"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="F82:H82"/>
+    <mergeCell ref="I82:J82"/>
+    <mergeCell ref="B83:E83"/>
+    <mergeCell ref="F83:H83"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="B74:E74"/>
+    <mergeCell ref="F74:H74"/>
+    <mergeCell ref="I74:J74"/>
+    <mergeCell ref="B75:E75"/>
+    <mergeCell ref="F75:H75"/>
+    <mergeCell ref="I75:J75"/>
+    <mergeCell ref="B79:E79"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="I79:J79"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="F86:H86"/>
+    <mergeCell ref="I86:J86"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="F87:H87"/>
+    <mergeCell ref="I87:J87"/>
+    <mergeCell ref="B84:E84"/>
+    <mergeCell ref="F84:H84"/>
+    <mergeCell ref="I84:J84"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="F85:H85"/>
+    <mergeCell ref="I85:J85"/>
+    <mergeCell ref="B95:E95"/>
+    <mergeCell ref="F95:H95"/>
+    <mergeCell ref="I95:J95"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="F96:H96"/>
+    <mergeCell ref="I96:J96"/>
+    <mergeCell ref="B93:E93"/>
+    <mergeCell ref="F93:H93"/>
+    <mergeCell ref="I93:J93"/>
+    <mergeCell ref="B94:E94"/>
+    <mergeCell ref="F94:H94"/>
+    <mergeCell ref="I94:J94"/>
+    <mergeCell ref="B105:J105"/>
+    <mergeCell ref="B106:J106"/>
+    <mergeCell ref="B99:E99"/>
+    <mergeCell ref="F99:H99"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="B103:D103"/>
+    <mergeCell ref="F103:I103"/>
+    <mergeCell ref="B104:J104"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="F97:H97"/>
+    <mergeCell ref="I97:J97"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="F98:H98"/>
+    <mergeCell ref="I98:J98"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/templates/hemodialysis_list_veícs_template.xlsx
+++ b/templates/hemodialysis_list_veícs_template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\F. Martins\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3A9CC0C7-51D3-4F66-A72F-23C7ED3D68AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF7FBAF7-F878-49C7-BB89-B40633474540}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{9FA8002F-7B96-42FD-9428-F3AD62B1682C}"/>
+    <workbookView xWindow="2460" yWindow="2460" windowWidth="21600" windowHeight="11385" xr2:uid="{9FA8002F-7B96-42FD-9428-F3AD62B1682C}"/>
   </bookViews>
   <sheets>
     <sheet name="Folha1" sheetId="1" r:id="rId1"/>
@@ -375,51 +375,42 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -447,51 +438,60 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left" vertical="center"/>
       <protection locked="0"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -564,53 +564,8 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>448862</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>90475</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4850210" cy="102077"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="6" name="Imagem 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C49DA30-1BA5-4396-98DA-1D475BC1F293}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="544112" y="8662975"/>
-          <a:ext cx="4850210" cy="102077"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>448862</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>175812</xdr:colOff>
       <xdr:row>49</xdr:row>
       <xdr:rowOff>90475</xdr:rowOff>
     </xdr:from>
@@ -642,7 +597,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="544112" y="8662975"/>
+          <a:off x="175812" y="8828075"/>
           <a:ext cx="4850210" cy="102077"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -794,8 +749,98 @@
   </xdr:oneCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>175812</xdr:colOff>
+      <xdr:row>102</xdr:row>
+      <xdr:rowOff>90475</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4850210" cy="102077"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Imagem 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D40D902-702D-49C5-9124-8479915D5CB7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="175812" y="18162575"/>
+          <a:ext cx="4850210" cy="102077"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>448862</xdr:colOff>
+      <xdr:colOff>582212</xdr:colOff>
+      <xdr:row>49</xdr:row>
+      <xdr:rowOff>90475</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="4850210" cy="102077"/>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="Imagem 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C49DA30-1BA5-4396-98DA-1D475BC1F293}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
+          <a:extLst>
+            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+            </a:ext>
+          </a:extLst>
+        </a:blip>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="772712" y="8828075"/>
+          <a:ext cx="4850210" cy="102077"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>582212</xdr:colOff>
       <xdr:row>102</xdr:row>
       <xdr:rowOff>90475</xdr:rowOff>
     </xdr:from>
@@ -827,52 +872,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="639362" y="8783625"/>
-          <a:ext cx="4850210" cy="102077"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>448862</xdr:colOff>
-      <xdr:row>102</xdr:row>
-      <xdr:rowOff>90475</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="4850210" cy="102077"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="12" name="Imagem 11">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3D40D902-702D-49C5-9124-8479915D5CB7}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2" cstate="print">
-          <a:extLst>
-            <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
-            </a:ext>
-          </a:extLst>
-        </a:blip>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="639362" y="8783625"/>
+          <a:off x="772712" y="18162575"/>
           <a:ext cx="4850210" cy="102077"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -1221,85 +1221,85 @@
   <sheetData>
     <row r="1" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="6" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C6" s="27"/>
-      <c r="D6" s="27"/>
-      <c r="E6" s="27"/>
-      <c r="F6" s="27"/>
-      <c r="G6" s="27"/>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="27"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="5"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
     </row>
     <row r="7" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="8" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B8" s="18" t="s">
+      <c r="B8" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="C8" s="19"/>
-      <c r="D8" s="19"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="19"/>
-      <c r="G8" s="19"/>
-      <c r="H8" s="19"/>
-      <c r="I8" s="19"/>
-      <c r="J8" s="20"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+      <c r="J8" s="17"/>
     </row>
     <row r="9" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B9" s="21"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="23"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="19"/>
+      <c r="I9" s="19"/>
+      <c r="J9" s="20"/>
     </row>
     <row r="10" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="24"/>
-      <c r="C10" s="25"/>
-      <c r="D10" s="25"/>
-      <c r="E10" s="25"/>
-      <c r="F10" s="25"/>
-      <c r="G10" s="25"/>
-      <c r="H10" s="25"/>
-      <c r="I10" s="25"/>
-      <c r="J10" s="26"/>
+      <c r="B10" s="21"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="23"/>
     </row>
     <row r="11" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="12" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="17" t="s">
+      <c r="B12" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="17"/>
-      <c r="F12" s="17"/>
-      <c r="G12" s="17"/>
-      <c r="H12" s="17"/>
-      <c r="I12" s="17"/>
-      <c r="J12" s="17"/>
+      <c r="C12" s="13"/>
+      <c r="D12" s="13"/>
+      <c r="E12" s="13"/>
+      <c r="F12" s="13"/>
+      <c r="G12" s="13"/>
+      <c r="H12" s="13"/>
+      <c r="I12" s="13"/>
+      <c r="J12" s="13"/>
     </row>
     <row r="13" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="14" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="16"/>
-      <c r="E14" s="16"/>
-      <c r="F14" s="16" t="s">
+      <c r="C14" s="12"/>
+      <c r="D14" s="12"/>
+      <c r="E14" s="12"/>
+      <c r="F14" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="G14" s="16"/>
-      <c r="H14" s="16"/>
-      <c r="I14" s="16" t="s">
+      <c r="G14" s="12"/>
+      <c r="H14" s="12"/>
+      <c r="I14" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="J14" s="16"/>
+      <c r="J14" s="12"/>
     </row>
     <row r="15" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="2"/>
@@ -1313,81 +1313,81 @@
       <c r="J15" s="2"/>
     </row>
     <row r="16" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B16" s="30"/>
-      <c r="C16" s="30"/>
-      <c r="D16" s="30"/>
-      <c r="E16" s="30"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="31"/>
-      <c r="I16" s="32"/>
-      <c r="J16" s="32"/>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="26"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="24"/>
     </row>
     <row r="17" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B17" s="12"/>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="33"/>
-      <c r="G17" s="33"/>
-      <c r="H17" s="33"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="34"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="27"/>
+      <c r="G17" s="27"/>
+      <c r="H17" s="27"/>
+      <c r="I17" s="11"/>
+      <c r="J17" s="11"/>
     </row>
     <row r="18" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="12"/>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="33"/>
-      <c r="G18" s="33"/>
-      <c r="H18" s="33"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="34"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="27"/>
+      <c r="G18" s="27"/>
+      <c r="H18" s="27"/>
+      <c r="I18" s="11"/>
+      <c r="J18" s="11"/>
     </row>
     <row r="19" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B19" s="12"/>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="33"/>
-      <c r="G19" s="33"/>
-      <c r="H19" s="33"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="34"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="27"/>
+      <c r="G19" s="27"/>
+      <c r="H19" s="27"/>
+      <c r="I19" s="11"/>
+      <c r="J19" s="11"/>
     </row>
     <row r="20" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="11"/>
-      <c r="C20" s="11"/>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="33"/>
-      <c r="G20" s="33"/>
-      <c r="H20" s="33"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="34"/>
+      <c r="B20" s="10"/>
+      <c r="C20" s="10"/>
+      <c r="D20" s="10"/>
+      <c r="E20" s="10"/>
+      <c r="F20" s="27"/>
+      <c r="G20" s="27"/>
+      <c r="H20" s="27"/>
+      <c r="I20" s="11"/>
+      <c r="J20" s="11"/>
     </row>
     <row r="21" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B21" s="11"/>
-      <c r="C21" s="11"/>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11"/>
-      <c r="F21" s="33"/>
-      <c r="G21" s="33"/>
-      <c r="H21" s="33"/>
-      <c r="I21" s="34"/>
-      <c r="J21" s="34"/>
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="27"/>
+      <c r="G21" s="27"/>
+      <c r="H21" s="27"/>
+      <c r="I21" s="11"/>
+      <c r="J21" s="11"/>
     </row>
     <row r="22" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="35"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="35"/>
-      <c r="I22" s="36"/>
-      <c r="J22" s="36"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="28"/>
+      <c r="G22" s="28"/>
+      <c r="H22" s="28"/>
+      <c r="I22" s="29"/>
+      <c r="J22" s="29"/>
     </row>
     <row r="23" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B23" s="4"/>
@@ -1401,113 +1401,113 @@
       <c r="J23" s="4"/>
     </row>
     <row r="24" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B24" s="17" t="s">
+      <c r="B24" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C24" s="17"/>
-      <c r="D24" s="17"/>
-      <c r="E24" s="17"/>
-      <c r="F24" s="17"/>
-      <c r="G24" s="17"/>
-      <c r="H24" s="17"/>
-      <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
+      <c r="C24" s="13"/>
+      <c r="D24" s="13"/>
+      <c r="E24" s="13"/>
+      <c r="F24" s="13"/>
+      <c r="G24" s="13"/>
+      <c r="H24" s="13"/>
+      <c r="I24" s="13"/>
+      <c r="J24" s="13"/>
     </row>
     <row r="25" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="26" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="16" t="s">
+      <c r="B26" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C26" s="16"/>
-      <c r="D26" s="16"/>
-      <c r="E26" s="16"/>
-      <c r="F26" s="16" t="s">
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="G26" s="16"/>
-      <c r="H26" s="16"/>
-      <c r="I26" s="16" t="s">
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="J26" s="16"/>
+      <c r="J26" s="12"/>
     </row>
     <row r="27" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="28" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="13"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="15"/>
-      <c r="F28" s="37"/>
-      <c r="G28" s="38"/>
-      <c r="H28" s="39"/>
-      <c r="I28" s="40"/>
-      <c r="J28" s="41"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="7"/>
+      <c r="D28" s="7"/>
+      <c r="E28" s="8"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="31"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="33"/>
+      <c r="J28" s="34"/>
     </row>
     <row r="29" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B29" s="12"/>
-      <c r="C29" s="12"/>
-      <c r="D29" s="12"/>
-      <c r="E29" s="12"/>
-      <c r="F29" s="33"/>
-      <c r="G29" s="33"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="34"/>
-      <c r="J29" s="34"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="27"/>
+      <c r="G29" s="27"/>
+      <c r="H29" s="27"/>
+      <c r="I29" s="11"/>
+      <c r="J29" s="11"/>
     </row>
     <row r="30" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B30" s="12"/>
-      <c r="C30" s="12"/>
-      <c r="D30" s="12"/>
-      <c r="E30" s="12"/>
-      <c r="F30" s="33"/>
-      <c r="G30" s="33"/>
-      <c r="H30" s="33"/>
-      <c r="I30" s="34"/>
-      <c r="J30" s="34"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="27"/>
+      <c r="G30" s="27"/>
+      <c r="H30" s="27"/>
+      <c r="I30" s="11"/>
+      <c r="J30" s="11"/>
     </row>
     <row r="31" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B31" s="12"/>
-      <c r="C31" s="12"/>
-      <c r="D31" s="12"/>
-      <c r="E31" s="12"/>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="34"/>
-      <c r="J31" s="34"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="27"/>
+      <c r="G31" s="27"/>
+      <c r="H31" s="27"/>
+      <c r="I31" s="11"/>
+      <c r="J31" s="11"/>
     </row>
     <row r="32" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B32" s="11"/>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="33"/>
-      <c r="G32" s="33"/>
-      <c r="H32" s="33"/>
-      <c r="I32" s="34"/>
-      <c r="J32" s="34"/>
+      <c r="B32" s="10"/>
+      <c r="C32" s="10"/>
+      <c r="D32" s="10"/>
+      <c r="E32" s="10"/>
+      <c r="F32" s="27"/>
+      <c r="G32" s="27"/>
+      <c r="H32" s="27"/>
+      <c r="I32" s="11"/>
+      <c r="J32" s="11"/>
     </row>
     <row r="33" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B33" s="11"/>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="33"/>
-      <c r="G33" s="33"/>
-      <c r="H33" s="33"/>
-      <c r="I33" s="34"/>
-      <c r="J33" s="34"/>
+      <c r="B33" s="10"/>
+      <c r="C33" s="10"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="27"/>
+      <c r="G33" s="27"/>
+      <c r="H33" s="27"/>
+      <c r="I33" s="11"/>
+      <c r="J33" s="11"/>
     </row>
     <row r="34" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B34" s="7"/>
-      <c r="C34" s="7"/>
-      <c r="D34" s="7"/>
-      <c r="E34" s="7"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="35"/>
-      <c r="H34" s="35"/>
-      <c r="I34" s="36"/>
-      <c r="J34" s="36"/>
+      <c r="B34" s="14"/>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="28"/>
+      <c r="G34" s="28"/>
+      <c r="H34" s="28"/>
+      <c r="I34" s="29"/>
+      <c r="J34" s="29"/>
     </row>
     <row r="35" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B35" s="4"/>
@@ -1521,612 +1521,754 @@
       <c r="J35" s="4"/>
     </row>
     <row r="36" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B36" s="17" t="s">
+      <c r="B36" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C36" s="17"/>
-      <c r="D36" s="17"/>
-      <c r="E36" s="17"/>
-      <c r="F36" s="17"/>
-      <c r="G36" s="17"/>
-      <c r="H36" s="17"/>
-      <c r="I36" s="17"/>
-      <c r="J36" s="17"/>
+      <c r="C36" s="13"/>
+      <c r="D36" s="13"/>
+      <c r="E36" s="13"/>
+      <c r="F36" s="13"/>
+      <c r="G36" s="13"/>
+      <c r="H36" s="13"/>
+      <c r="I36" s="13"/>
+      <c r="J36" s="13"/>
     </row>
     <row r="37" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B38" s="16" t="s">
+      <c r="B38" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C38" s="16"/>
-      <c r="D38" s="16"/>
-      <c r="E38" s="16"/>
-      <c r="F38" s="16" t="s">
+      <c r="C38" s="12"/>
+      <c r="D38" s="12"/>
+      <c r="E38" s="12"/>
+      <c r="F38" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="G38" s="16"/>
-      <c r="H38" s="16"/>
-      <c r="I38" s="16" t="s">
+      <c r="G38" s="12"/>
+      <c r="H38" s="12"/>
+      <c r="I38" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="J38" s="16"/>
+      <c r="J38" s="12"/>
     </row>
     <row r="39" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="40" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B40" s="13"/>
-      <c r="C40" s="14"/>
-      <c r="D40" s="14"/>
-      <c r="E40" s="15"/>
-      <c r="F40" s="37"/>
-      <c r="G40" s="38"/>
-      <c r="H40" s="39"/>
-      <c r="I40" s="40"/>
-      <c r="J40" s="41"/>
+      <c r="B40" s="6"/>
+      <c r="C40" s="7"/>
+      <c r="D40" s="7"/>
+      <c r="E40" s="8"/>
+      <c r="F40" s="30"/>
+      <c r="G40" s="31"/>
+      <c r="H40" s="32"/>
+      <c r="I40" s="33"/>
+      <c r="J40" s="34"/>
     </row>
     <row r="41" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B41" s="12"/>
-      <c r="C41" s="12"/>
-      <c r="D41" s="12"/>
-      <c r="E41" s="12"/>
-      <c r="F41" s="33"/>
-      <c r="G41" s="33"/>
-      <c r="H41" s="33"/>
-      <c r="I41" s="34"/>
-      <c r="J41" s="34"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
+      <c r="F41" s="27"/>
+      <c r="G41" s="27"/>
+      <c r="H41" s="27"/>
+      <c r="I41" s="11"/>
+      <c r="J41" s="11"/>
     </row>
     <row r="42" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B42" s="12"/>
-      <c r="C42" s="12"/>
-      <c r="D42" s="12"/>
-      <c r="E42" s="12"/>
-      <c r="F42" s="33"/>
-      <c r="G42" s="33"/>
-      <c r="H42" s="33"/>
-      <c r="I42" s="34"/>
-      <c r="J42" s="34"/>
+      <c r="B42" s="9"/>
+      <c r="C42" s="9"/>
+      <c r="D42" s="9"/>
+      <c r="E42" s="9"/>
+      <c r="F42" s="27"/>
+      <c r="G42" s="27"/>
+      <c r="H42" s="27"/>
+      <c r="I42" s="11"/>
+      <c r="J42" s="11"/>
     </row>
     <row r="43" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B43" s="12"/>
-      <c r="C43" s="12"/>
-      <c r="D43" s="12"/>
-      <c r="E43" s="12"/>
-      <c r="F43" s="33"/>
-      <c r="G43" s="33"/>
-      <c r="H43" s="33"/>
-      <c r="I43" s="34"/>
-      <c r="J43" s="34"/>
+      <c r="B43" s="9"/>
+      <c r="C43" s="9"/>
+      <c r="D43" s="9"/>
+      <c r="E43" s="9"/>
+      <c r="F43" s="27"/>
+      <c r="G43" s="27"/>
+      <c r="H43" s="27"/>
+      <c r="I43" s="11"/>
+      <c r="J43" s="11"/>
     </row>
     <row r="44" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B44" s="11"/>
-      <c r="C44" s="11"/>
-      <c r="D44" s="11"/>
-      <c r="E44" s="11"/>
-      <c r="F44" s="33"/>
-      <c r="G44" s="33"/>
-      <c r="H44" s="33"/>
-      <c r="I44" s="34"/>
-      <c r="J44" s="34"/>
+      <c r="B44" s="10"/>
+      <c r="C44" s="10"/>
+      <c r="D44" s="10"/>
+      <c r="E44" s="10"/>
+      <c r="F44" s="27"/>
+      <c r="G44" s="27"/>
+      <c r="H44" s="27"/>
+      <c r="I44" s="11"/>
+      <c r="J44" s="11"/>
     </row>
     <row r="45" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B45" s="11"/>
-      <c r="C45" s="11"/>
-      <c r="D45" s="11"/>
-      <c r="E45" s="11"/>
-      <c r="F45" s="33"/>
-      <c r="G45" s="33"/>
-      <c r="H45" s="33"/>
-      <c r="I45" s="34"/>
-      <c r="J45" s="34"/>
+      <c r="B45" s="10"/>
+      <c r="C45" s="10"/>
+      <c r="D45" s="10"/>
+      <c r="E45" s="10"/>
+      <c r="F45" s="27"/>
+      <c r="G45" s="27"/>
+      <c r="H45" s="27"/>
+      <c r="I45" s="11"/>
+      <c r="J45" s="11"/>
     </row>
     <row r="46" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B46" s="7"/>
-      <c r="C46" s="7"/>
-      <c r="D46" s="7"/>
-      <c r="E46" s="7"/>
-      <c r="F46" s="35"/>
-      <c r="G46" s="35"/>
-      <c r="H46" s="35"/>
-      <c r="I46" s="36"/>
-      <c r="J46" s="36"/>
+      <c r="B46" s="14"/>
+      <c r="C46" s="14"/>
+      <c r="D46" s="14"/>
+      <c r="E46" s="14"/>
+      <c r="F46" s="28"/>
+      <c r="G46" s="28"/>
+      <c r="H46" s="28"/>
+      <c r="I46" s="29"/>
+      <c r="J46" s="29"/>
     </row>
     <row r="47" spans="2:10" ht="8.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B47" s="28"/>
-      <c r="C47" s="28"/>
-      <c r="D47" s="28"/>
-      <c r="E47" s="29"/>
-      <c r="F47" s="29"/>
-      <c r="G47" s="29"/>
-      <c r="H47" s="29"/>
-      <c r="I47" s="29"/>
+      <c r="B47" s="40"/>
+      <c r="C47" s="40"/>
+      <c r="D47" s="40"/>
+      <c r="E47" s="41"/>
+      <c r="F47" s="41"/>
+      <c r="G47" s="41"/>
+      <c r="H47" s="41"/>
+      <c r="I47" s="41"/>
       <c r="J47" s="3"/>
     </row>
     <row r="48" spans="2:10" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="49" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="50" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B50" s="8"/>
-      <c r="C50" s="8"/>
-      <c r="D50" s="8"/>
+      <c r="B50" s="35"/>
+      <c r="C50" s="35"/>
+      <c r="D50" s="35"/>
       <c r="E50" s="1"/>
-      <c r="F50" s="9"/>
-      <c r="G50" s="9"/>
-      <c r="H50" s="9"/>
-      <c r="I50" s="9"/>
+      <c r="F50" s="36"/>
+      <c r="G50" s="36"/>
+      <c r="H50" s="36"/>
+      <c r="I50" s="36"/>
       <c r="J50" s="1"/>
     </row>
     <row r="51" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B51" s="10" t="s">
+      <c r="B51" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="C51" s="10"/>
-      <c r="D51" s="10"/>
-      <c r="E51" s="10"/>
-      <c r="F51" s="10"/>
-      <c r="G51" s="10"/>
-      <c r="H51" s="10"/>
-      <c r="I51" s="10"/>
-      <c r="J51" s="10"/>
+      <c r="C51" s="37"/>
+      <c r="D51" s="37"/>
+      <c r="E51" s="37"/>
+      <c r="F51" s="37"/>
+      <c r="G51" s="37"/>
+      <c r="H51" s="37"/>
+      <c r="I51" s="37"/>
+      <c r="J51" s="37"/>
     </row>
     <row r="52" spans="2:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="C52" s="5"/>
-      <c r="D52" s="5"/>
-      <c r="E52" s="5"/>
-      <c r="F52" s="5"/>
-      <c r="G52" s="5"/>
-      <c r="H52" s="5"/>
-      <c r="I52" s="5"/>
-      <c r="J52" s="5"/>
+      <c r="C52" s="38"/>
+      <c r="D52" s="38"/>
+      <c r="E52" s="38"/>
+      <c r="F52" s="38"/>
+      <c r="G52" s="38"/>
+      <c r="H52" s="38"/>
+      <c r="I52" s="38"/>
+      <c r="J52" s="38"/>
     </row>
     <row r="53" spans="2:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B53" s="6" t="s">
+      <c r="B53" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="C53" s="6"/>
-      <c r="D53" s="6"/>
-      <c r="E53" s="6"/>
-      <c r="F53" s="6"/>
-      <c r="G53" s="6"/>
-      <c r="H53" s="6"/>
-      <c r="I53" s="6"/>
-      <c r="J53" s="6"/>
+      <c r="C53" s="39"/>
+      <c r="D53" s="39"/>
+      <c r="E53" s="39"/>
+      <c r="F53" s="39"/>
+      <c r="G53" s="39"/>
+      <c r="H53" s="39"/>
+      <c r="I53" s="39"/>
+      <c r="J53" s="39"/>
     </row>
     <row r="54" spans="2:10" ht="7.5" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="59" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B59" s="27" t="s">
+      <c r="B59" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="C59" s="27"/>
-      <c r="D59" s="27"/>
-      <c r="E59" s="27"/>
-      <c r="F59" s="27"/>
-      <c r="G59" s="27"/>
-      <c r="H59" s="27"/>
-      <c r="I59" s="27"/>
-      <c r="J59" s="27"/>
+      <c r="C59" s="5"/>
+      <c r="D59" s="5"/>
+      <c r="E59" s="5"/>
+      <c r="F59" s="5"/>
+      <c r="G59" s="5"/>
+      <c r="H59" s="5"/>
+      <c r="I59" s="5"/>
+      <c r="J59" s="5"/>
     </row>
     <row r="60" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="61" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B61" s="18" t="s">
+      <c r="B61" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C61" s="19"/>
-      <c r="D61" s="19"/>
-      <c r="E61" s="19"/>
-      <c r="F61" s="19"/>
-      <c r="G61" s="19"/>
-      <c r="H61" s="19"/>
-      <c r="I61" s="19"/>
-      <c r="J61" s="20"/>
+      <c r="C61" s="16"/>
+      <c r="D61" s="16"/>
+      <c r="E61" s="16"/>
+      <c r="F61" s="16"/>
+      <c r="G61" s="16"/>
+      <c r="H61" s="16"/>
+      <c r="I61" s="16"/>
+      <c r="J61" s="17"/>
     </row>
     <row r="62" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B62" s="21"/>
-      <c r="C62" s="22"/>
-      <c r="D62" s="22"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="22"/>
-      <c r="H62" s="22"/>
-      <c r="I62" s="22"/>
-      <c r="J62" s="23"/>
+      <c r="B62" s="18"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="19"/>
+      <c r="E62" s="19"/>
+      <c r="F62" s="19"/>
+      <c r="G62" s="19"/>
+      <c r="H62" s="19"/>
+      <c r="I62" s="19"/>
+      <c r="J62" s="20"/>
     </row>
     <row r="63" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B63" s="24"/>
-      <c r="C63" s="25"/>
-      <c r="D63" s="25"/>
-      <c r="E63" s="25"/>
-      <c r="F63" s="25"/>
-      <c r="G63" s="25"/>
-      <c r="H63" s="25"/>
-      <c r="I63" s="25"/>
-      <c r="J63" s="26"/>
+      <c r="B63" s="21"/>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="22"/>
+      <c r="G63" s="22"/>
+      <c r="H63" s="22"/>
+      <c r="I63" s="22"/>
+      <c r="J63" s="23"/>
     </row>
     <row r="64" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="65" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B65" s="17" t="s">
+      <c r="B65" s="13" t="s">
         <v>1</v>
       </c>
-      <c r="C65" s="17"/>
-      <c r="D65" s="17"/>
-      <c r="E65" s="17"/>
-      <c r="F65" s="17"/>
-      <c r="G65" s="17"/>
-      <c r="H65" s="17"/>
-      <c r="I65" s="17"/>
-      <c r="J65" s="17"/>
+      <c r="C65" s="13"/>
+      <c r="D65" s="13"/>
+      <c r="E65" s="13"/>
+      <c r="F65" s="13"/>
+      <c r="G65" s="13"/>
+      <c r="H65" s="13"/>
+      <c r="I65" s="13"/>
+      <c r="J65" s="13"/>
     </row>
     <row r="66" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="67" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B67" s="16" t="s">
+      <c r="B67" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C67" s="16"/>
-      <c r="D67" s="16"/>
-      <c r="E67" s="16"/>
-      <c r="F67" s="16" t="s">
+      <c r="C67" s="12"/>
+      <c r="D67" s="12"/>
+      <c r="E67" s="12"/>
+      <c r="F67" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="G67" s="16"/>
-      <c r="H67" s="16"/>
-      <c r="I67" s="16" t="s">
+      <c r="G67" s="12"/>
+      <c r="H67" s="12"/>
+      <c r="I67" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="J67" s="16"/>
+      <c r="J67" s="12"/>
     </row>
     <row r="68" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="69" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B69" s="13"/>
-      <c r="C69" s="14"/>
-      <c r="D69" s="14"/>
-      <c r="E69" s="15"/>
-      <c r="F69" s="37"/>
-      <c r="G69" s="38"/>
-      <c r="H69" s="39"/>
-      <c r="I69" s="40"/>
-      <c r="J69" s="41"/>
+      <c r="B69" s="6"/>
+      <c r="C69" s="7"/>
+      <c r="D69" s="7"/>
+      <c r="E69" s="8"/>
+      <c r="F69" s="30"/>
+      <c r="G69" s="31"/>
+      <c r="H69" s="32"/>
+      <c r="I69" s="33"/>
+      <c r="J69" s="34"/>
     </row>
     <row r="70" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B70" s="12"/>
-      <c r="C70" s="12"/>
-      <c r="D70" s="12"/>
-      <c r="E70" s="12"/>
-      <c r="F70" s="33"/>
-      <c r="G70" s="33"/>
-      <c r="H70" s="33"/>
-      <c r="I70" s="34"/>
-      <c r="J70" s="34"/>
+      <c r="B70" s="9"/>
+      <c r="C70" s="9"/>
+      <c r="D70" s="9"/>
+      <c r="E70" s="9"/>
+      <c r="F70" s="27"/>
+      <c r="G70" s="27"/>
+      <c r="H70" s="27"/>
+      <c r="I70" s="11"/>
+      <c r="J70" s="11"/>
     </row>
     <row r="71" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B71" s="12"/>
-      <c r="C71" s="12"/>
-      <c r="D71" s="12"/>
-      <c r="E71" s="12"/>
-      <c r="F71" s="33"/>
-      <c r="G71" s="33"/>
-      <c r="H71" s="33"/>
-      <c r="I71" s="34"/>
-      <c r="J71" s="34"/>
+      <c r="B71" s="9"/>
+      <c r="C71" s="9"/>
+      <c r="D71" s="9"/>
+      <c r="E71" s="9"/>
+      <c r="F71" s="27"/>
+      <c r="G71" s="27"/>
+      <c r="H71" s="27"/>
+      <c r="I71" s="11"/>
+      <c r="J71" s="11"/>
     </row>
     <row r="72" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B72" s="12"/>
-      <c r="C72" s="12"/>
-      <c r="D72" s="12"/>
-      <c r="E72" s="12"/>
-      <c r="F72" s="33"/>
-      <c r="G72" s="33"/>
-      <c r="H72" s="33"/>
-      <c r="I72" s="34"/>
-      <c r="J72" s="34"/>
+      <c r="B72" s="9"/>
+      <c r="C72" s="9"/>
+      <c r="D72" s="9"/>
+      <c r="E72" s="9"/>
+      <c r="F72" s="27"/>
+      <c r="G72" s="27"/>
+      <c r="H72" s="27"/>
+      <c r="I72" s="11"/>
+      <c r="J72" s="11"/>
     </row>
     <row r="73" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B73" s="11"/>
-      <c r="C73" s="11"/>
-      <c r="D73" s="11"/>
-      <c r="E73" s="11"/>
-      <c r="F73" s="33"/>
-      <c r="G73" s="33"/>
-      <c r="H73" s="33"/>
-      <c r="I73" s="34"/>
-      <c r="J73" s="34"/>
+      <c r="B73" s="10"/>
+      <c r="C73" s="10"/>
+      <c r="D73" s="10"/>
+      <c r="E73" s="10"/>
+      <c r="F73" s="27"/>
+      <c r="G73" s="27"/>
+      <c r="H73" s="27"/>
+      <c r="I73" s="11"/>
+      <c r="J73" s="11"/>
     </row>
     <row r="74" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B74" s="11"/>
-      <c r="C74" s="11"/>
-      <c r="D74" s="11"/>
-      <c r="E74" s="11"/>
-      <c r="F74" s="33"/>
-      <c r="G74" s="33"/>
-      <c r="H74" s="33"/>
-      <c r="I74" s="34"/>
-      <c r="J74" s="34"/>
+      <c r="B74" s="10"/>
+      <c r="C74" s="10"/>
+      <c r="D74" s="10"/>
+      <c r="E74" s="10"/>
+      <c r="F74" s="27"/>
+      <c r="G74" s="27"/>
+      <c r="H74" s="27"/>
+      <c r="I74" s="11"/>
+      <c r="J74" s="11"/>
     </row>
     <row r="75" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B75" s="7"/>
-      <c r="C75" s="7"/>
-      <c r="D75" s="7"/>
-      <c r="E75" s="7"/>
-      <c r="F75" s="35"/>
-      <c r="G75" s="35"/>
-      <c r="H75" s="35"/>
-      <c r="I75" s="36"/>
-      <c r="J75" s="36"/>
+      <c r="B75" s="14"/>
+      <c r="C75" s="14"/>
+      <c r="D75" s="14"/>
+      <c r="E75" s="14"/>
+      <c r="F75" s="28"/>
+      <c r="G75" s="28"/>
+      <c r="H75" s="28"/>
+      <c r="I75" s="29"/>
+      <c r="J75" s="29"/>
     </row>
     <row r="76" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="77" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B77" s="17" t="s">
+      <c r="B77" s="13" t="s">
         <v>2</v>
       </c>
-      <c r="C77" s="17"/>
-      <c r="D77" s="17"/>
-      <c r="E77" s="17"/>
-      <c r="F77" s="17"/>
-      <c r="G77" s="17"/>
-      <c r="H77" s="17"/>
-      <c r="I77" s="17"/>
-      <c r="J77" s="17"/>
+      <c r="C77" s="13"/>
+      <c r="D77" s="13"/>
+      <c r="E77" s="13"/>
+      <c r="F77" s="13"/>
+      <c r="G77" s="13"/>
+      <c r="H77" s="13"/>
+      <c r="I77" s="13"/>
+      <c r="J77" s="13"/>
     </row>
     <row r="78" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="79" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B79" s="16" t="s">
+      <c r="B79" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C79" s="16"/>
-      <c r="D79" s="16"/>
-      <c r="E79" s="16"/>
-      <c r="F79" s="16" t="s">
+      <c r="C79" s="12"/>
+      <c r="D79" s="12"/>
+      <c r="E79" s="12"/>
+      <c r="F79" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="G79" s="16"/>
-      <c r="H79" s="16"/>
-      <c r="I79" s="16" t="s">
+      <c r="G79" s="12"/>
+      <c r="H79" s="12"/>
+      <c r="I79" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="J79" s="16"/>
+      <c r="J79" s="12"/>
     </row>
     <row r="80" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="81" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B81" s="13"/>
-      <c r="C81" s="14"/>
-      <c r="D81" s="14"/>
-      <c r="E81" s="15"/>
-      <c r="F81" s="37"/>
-      <c r="G81" s="38"/>
-      <c r="H81" s="39"/>
-      <c r="I81" s="40"/>
-      <c r="J81" s="41"/>
+      <c r="B81" s="6"/>
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="8"/>
+      <c r="F81" s="30"/>
+      <c r="G81" s="31"/>
+      <c r="H81" s="32"/>
+      <c r="I81" s="33"/>
+      <c r="J81" s="34"/>
     </row>
     <row r="82" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B82" s="12"/>
-      <c r="C82" s="12"/>
-      <c r="D82" s="12"/>
-      <c r="E82" s="12"/>
-      <c r="F82" s="33"/>
-      <c r="G82" s="33"/>
-      <c r="H82" s="33"/>
-      <c r="I82" s="34"/>
-      <c r="J82" s="34"/>
+      <c r="B82" s="9"/>
+      <c r="C82" s="9"/>
+      <c r="D82" s="9"/>
+      <c r="E82" s="9"/>
+      <c r="F82" s="27"/>
+      <c r="G82" s="27"/>
+      <c r="H82" s="27"/>
+      <c r="I82" s="11"/>
+      <c r="J82" s="11"/>
     </row>
     <row r="83" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B83" s="12"/>
-      <c r="C83" s="12"/>
-      <c r="D83" s="12"/>
-      <c r="E83" s="12"/>
-      <c r="F83" s="33"/>
-      <c r="G83" s="33"/>
-      <c r="H83" s="33"/>
-      <c r="I83" s="34"/>
-      <c r="J83" s="34"/>
+      <c r="B83" s="9"/>
+      <c r="C83" s="9"/>
+      <c r="D83" s="9"/>
+      <c r="E83" s="9"/>
+      <c r="F83" s="27"/>
+      <c r="G83" s="27"/>
+      <c r="H83" s="27"/>
+      <c r="I83" s="11"/>
+      <c r="J83" s="11"/>
     </row>
     <row r="84" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B84" s="12"/>
-      <c r="C84" s="12"/>
-      <c r="D84" s="12"/>
-      <c r="E84" s="12"/>
-      <c r="F84" s="33"/>
-      <c r="G84" s="33"/>
-      <c r="H84" s="33"/>
-      <c r="I84" s="34"/>
-      <c r="J84" s="34"/>
+      <c r="B84" s="9"/>
+      <c r="C84" s="9"/>
+      <c r="D84" s="9"/>
+      <c r="E84" s="9"/>
+      <c r="F84" s="27"/>
+      <c r="G84" s="27"/>
+      <c r="H84" s="27"/>
+      <c r="I84" s="11"/>
+      <c r="J84" s="11"/>
     </row>
     <row r="85" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B85" s="11"/>
-      <c r="C85" s="11"/>
-      <c r="D85" s="11"/>
-      <c r="E85" s="11"/>
-      <c r="F85" s="33"/>
-      <c r="G85" s="33"/>
-      <c r="H85" s="33"/>
-      <c r="I85" s="34"/>
-      <c r="J85" s="34"/>
+      <c r="B85" s="10"/>
+      <c r="C85" s="10"/>
+      <c r="D85" s="10"/>
+      <c r="E85" s="10"/>
+      <c r="F85" s="27"/>
+      <c r="G85" s="27"/>
+      <c r="H85" s="27"/>
+      <c r="I85" s="11"/>
+      <c r="J85" s="11"/>
     </row>
     <row r="86" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B86" s="11"/>
-      <c r="C86" s="11"/>
-      <c r="D86" s="11"/>
-      <c r="E86" s="11"/>
-      <c r="F86" s="33"/>
-      <c r="G86" s="33"/>
-      <c r="H86" s="33"/>
-      <c r="I86" s="34"/>
-      <c r="J86" s="34"/>
+      <c r="B86" s="10"/>
+      <c r="C86" s="10"/>
+      <c r="D86" s="10"/>
+      <c r="E86" s="10"/>
+      <c r="F86" s="27"/>
+      <c r="G86" s="27"/>
+      <c r="H86" s="27"/>
+      <c r="I86" s="11"/>
+      <c r="J86" s="11"/>
     </row>
     <row r="87" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B87" s="7"/>
-      <c r="C87" s="7"/>
-      <c r="D87" s="7"/>
-      <c r="E87" s="7"/>
-      <c r="F87" s="35"/>
-      <c r="G87" s="35"/>
-      <c r="H87" s="35"/>
-      <c r="I87" s="36"/>
-      <c r="J87" s="36"/>
+      <c r="B87" s="14"/>
+      <c r="C87" s="14"/>
+      <c r="D87" s="14"/>
+      <c r="E87" s="14"/>
+      <c r="F87" s="28"/>
+      <c r="G87" s="28"/>
+      <c r="H87" s="28"/>
+      <c r="I87" s="29"/>
+      <c r="J87" s="29"/>
     </row>
     <row r="88" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="89" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B89" s="17" t="s">
+      <c r="B89" s="13" t="s">
         <v>3</v>
       </c>
-      <c r="C89" s="17"/>
-      <c r="D89" s="17"/>
-      <c r="E89" s="17"/>
-      <c r="F89" s="17"/>
-      <c r="G89" s="17"/>
-      <c r="H89" s="17"/>
-      <c r="I89" s="17"/>
-      <c r="J89" s="17"/>
+      <c r="C89" s="13"/>
+      <c r="D89" s="13"/>
+      <c r="E89" s="13"/>
+      <c r="F89" s="13"/>
+      <c r="G89" s="13"/>
+      <c r="H89" s="13"/>
+      <c r="I89" s="13"/>
+      <c r="J89" s="13"/>
     </row>
     <row r="90" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="91" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B91" s="16" t="s">
+      <c r="B91" s="12" t="s">
         <v>5</v>
       </c>
-      <c r="C91" s="16"/>
-      <c r="D91" s="16"/>
-      <c r="E91" s="16"/>
-      <c r="F91" s="16" t="s">
+      <c r="C91" s="12"/>
+      <c r="D91" s="12"/>
+      <c r="E91" s="12"/>
+      <c r="F91" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="G91" s="16"/>
-      <c r="H91" s="16"/>
-      <c r="I91" s="16" t="s">
+      <c r="G91" s="12"/>
+      <c r="H91" s="12"/>
+      <c r="I91" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="J91" s="16"/>
+      <c r="J91" s="12"/>
     </row>
     <row r="92" spans="2:10" ht="3.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="93" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B93" s="13"/>
-      <c r="C93" s="14"/>
-      <c r="D93" s="14"/>
-      <c r="E93" s="15"/>
-      <c r="F93" s="37"/>
-      <c r="G93" s="38"/>
-      <c r="H93" s="39"/>
-      <c r="I93" s="40"/>
-      <c r="J93" s="41"/>
+      <c r="B93" s="6"/>
+      <c r="C93" s="7"/>
+      <c r="D93" s="7"/>
+      <c r="E93" s="8"/>
+      <c r="F93" s="30"/>
+      <c r="G93" s="31"/>
+      <c r="H93" s="32"/>
+      <c r="I93" s="33"/>
+      <c r="J93" s="34"/>
     </row>
     <row r="94" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B94" s="12"/>
-      <c r="C94" s="12"/>
-      <c r="D94" s="12"/>
-      <c r="E94" s="12"/>
-      <c r="F94" s="33"/>
-      <c r="G94" s="33"/>
-      <c r="H94" s="33"/>
-      <c r="I94" s="34"/>
-      <c r="J94" s="34"/>
+      <c r="B94" s="9"/>
+      <c r="C94" s="9"/>
+      <c r="D94" s="9"/>
+      <c r="E94" s="9"/>
+      <c r="F94" s="27"/>
+      <c r="G94" s="27"/>
+      <c r="H94" s="27"/>
+      <c r="I94" s="11"/>
+      <c r="J94" s="11"/>
     </row>
     <row r="95" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B95" s="12"/>
-      <c r="C95" s="12"/>
-      <c r="D95" s="12"/>
-      <c r="E95" s="12"/>
-      <c r="F95" s="33"/>
-      <c r="G95" s="33"/>
-      <c r="H95" s="33"/>
-      <c r="I95" s="34"/>
-      <c r="J95" s="34"/>
+      <c r="B95" s="9"/>
+      <c r="C95" s="9"/>
+      <c r="D95" s="9"/>
+      <c r="E95" s="9"/>
+      <c r="F95" s="27"/>
+      <c r="G95" s="27"/>
+      <c r="H95" s="27"/>
+      <c r="I95" s="11"/>
+      <c r="J95" s="11"/>
     </row>
     <row r="96" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B96" s="12"/>
-      <c r="C96" s="12"/>
-      <c r="D96" s="12"/>
-      <c r="E96" s="12"/>
-      <c r="F96" s="33"/>
-      <c r="G96" s="33"/>
-      <c r="H96" s="33"/>
-      <c r="I96" s="34"/>
-      <c r="J96" s="34"/>
+      <c r="B96" s="9"/>
+      <c r="C96" s="9"/>
+      <c r="D96" s="9"/>
+      <c r="E96" s="9"/>
+      <c r="F96" s="27"/>
+      <c r="G96" s="27"/>
+      <c r="H96" s="27"/>
+      <c r="I96" s="11"/>
+      <c r="J96" s="11"/>
     </row>
     <row r="97" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B97" s="11"/>
-      <c r="C97" s="11"/>
-      <c r="D97" s="11"/>
-      <c r="E97" s="11"/>
-      <c r="F97" s="33"/>
-      <c r="G97" s="33"/>
-      <c r="H97" s="33"/>
-      <c r="I97" s="34"/>
-      <c r="J97" s="34"/>
+      <c r="B97" s="10"/>
+      <c r="C97" s="10"/>
+      <c r="D97" s="10"/>
+      <c r="E97" s="10"/>
+      <c r="F97" s="27"/>
+      <c r="G97" s="27"/>
+      <c r="H97" s="27"/>
+      <c r="I97" s="11"/>
+      <c r="J97" s="11"/>
     </row>
     <row r="98" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B98" s="11"/>
-      <c r="C98" s="11"/>
-      <c r="D98" s="11"/>
-      <c r="E98" s="11"/>
-      <c r="F98" s="33"/>
-      <c r="G98" s="33"/>
-      <c r="H98" s="33"/>
-      <c r="I98" s="34"/>
-      <c r="J98" s="34"/>
+      <c r="B98" s="10"/>
+      <c r="C98" s="10"/>
+      <c r="D98" s="10"/>
+      <c r="E98" s="10"/>
+      <c r="F98" s="27"/>
+      <c r="G98" s="27"/>
+      <c r="H98" s="27"/>
+      <c r="I98" s="11"/>
+      <c r="J98" s="11"/>
     </row>
     <row r="99" spans="2:10" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B99" s="7"/>
-      <c r="C99" s="7"/>
-      <c r="D99" s="7"/>
-      <c r="E99" s="7"/>
-      <c r="F99" s="35"/>
-      <c r="G99" s="35"/>
-      <c r="H99" s="35"/>
-      <c r="I99" s="36"/>
-      <c r="J99" s="36"/>
+      <c r="B99" s="14"/>
+      <c r="C99" s="14"/>
+      <c r="D99" s="14"/>
+      <c r="E99" s="14"/>
+      <c r="F99" s="28"/>
+      <c r="G99" s="28"/>
+      <c r="H99" s="28"/>
+      <c r="I99" s="29"/>
+      <c r="J99" s="29"/>
     </row>
     <row r="100" spans="2:10" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="101" spans="2:10" ht="8.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="102" spans="2:10" ht="9" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="103" spans="2:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="B103" s="8"/>
-      <c r="C103" s="8"/>
-      <c r="D103" s="8"/>
+      <c r="B103" s="35"/>
+      <c r="C103" s="35"/>
+      <c r="D103" s="35"/>
       <c r="E103" s="1"/>
-      <c r="F103" s="9"/>
-      <c r="G103" s="9"/>
-      <c r="H103" s="9"/>
-      <c r="I103" s="9"/>
+      <c r="F103" s="36"/>
+      <c r="G103" s="36"/>
+      <c r="H103" s="36"/>
+      <c r="I103" s="36"/>
       <c r="J103" s="1"/>
     </row>
     <row r="104" spans="2:10" ht="11.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B104" s="10" t="s">
+      <c r="B104" s="37" t="s">
         <v>8</v>
       </c>
-      <c r="C104" s="10"/>
-      <c r="D104" s="10"/>
-      <c r="E104" s="10"/>
-      <c r="F104" s="10"/>
-      <c r="G104" s="10"/>
-      <c r="H104" s="10"/>
-      <c r="I104" s="10"/>
-      <c r="J104" s="10"/>
+      <c r="C104" s="37"/>
+      <c r="D104" s="37"/>
+      <c r="E104" s="37"/>
+      <c r="F104" s="37"/>
+      <c r="G104" s="37"/>
+      <c r="H104" s="37"/>
+      <c r="I104" s="37"/>
+      <c r="J104" s="37"/>
     </row>
     <row r="105" spans="2:10" ht="10.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B105" s="5" t="s">
+      <c r="B105" s="38" t="s">
         <v>9</v>
       </c>
-      <c r="C105" s="5"/>
-      <c r="D105" s="5"/>
-      <c r="E105" s="5"/>
-      <c r="F105" s="5"/>
-      <c r="G105" s="5"/>
-      <c r="H105" s="5"/>
-      <c r="I105" s="5"/>
-      <c r="J105" s="5"/>
+      <c r="C105" s="38"/>
+      <c r="D105" s="38"/>
+      <c r="E105" s="38"/>
+      <c r="F105" s="38"/>
+      <c r="G105" s="38"/>
+      <c r="H105" s="38"/>
+      <c r="I105" s="38"/>
+      <c r="J105" s="38"/>
     </row>
     <row r="106" spans="2:10" ht="9.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B106" s="6" t="s">
+      <c r="B106" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="C106" s="6"/>
-      <c r="D106" s="6"/>
-      <c r="E106" s="6"/>
-      <c r="F106" s="6"/>
-      <c r="G106" s="6"/>
-      <c r="H106" s="6"/>
-      <c r="I106" s="6"/>
-      <c r="J106" s="6"/>
+      <c r="C106" s="39"/>
+      <c r="D106" s="39"/>
+      <c r="E106" s="39"/>
+      <c r="F106" s="39"/>
+      <c r="G106" s="39"/>
+      <c r="H106" s="39"/>
+      <c r="I106" s="39"/>
+      <c r="J106" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="166">
+    <mergeCell ref="B105:J105"/>
+    <mergeCell ref="B106:J106"/>
+    <mergeCell ref="B99:E99"/>
+    <mergeCell ref="F99:H99"/>
+    <mergeCell ref="I99:J99"/>
+    <mergeCell ref="B103:D103"/>
+    <mergeCell ref="F103:I103"/>
+    <mergeCell ref="B104:J104"/>
+    <mergeCell ref="B97:E97"/>
+    <mergeCell ref="F97:H97"/>
+    <mergeCell ref="I97:J97"/>
+    <mergeCell ref="B98:E98"/>
+    <mergeCell ref="F98:H98"/>
+    <mergeCell ref="I98:J98"/>
+    <mergeCell ref="B95:E95"/>
+    <mergeCell ref="F95:H95"/>
+    <mergeCell ref="I95:J95"/>
+    <mergeCell ref="B96:E96"/>
+    <mergeCell ref="F96:H96"/>
+    <mergeCell ref="I96:J96"/>
+    <mergeCell ref="B93:E93"/>
+    <mergeCell ref="F93:H93"/>
+    <mergeCell ref="I93:J93"/>
+    <mergeCell ref="B94:E94"/>
+    <mergeCell ref="F94:H94"/>
+    <mergeCell ref="I94:J94"/>
+    <mergeCell ref="B86:E86"/>
+    <mergeCell ref="F86:H86"/>
+    <mergeCell ref="I86:J86"/>
+    <mergeCell ref="B87:E87"/>
+    <mergeCell ref="F87:H87"/>
+    <mergeCell ref="I87:J87"/>
+    <mergeCell ref="B84:E84"/>
+    <mergeCell ref="F84:H84"/>
+    <mergeCell ref="I84:J84"/>
+    <mergeCell ref="B85:E85"/>
+    <mergeCell ref="F85:H85"/>
+    <mergeCell ref="I85:J85"/>
+    <mergeCell ref="I70:J70"/>
+    <mergeCell ref="B71:E71"/>
+    <mergeCell ref="F71:H71"/>
+    <mergeCell ref="I71:J71"/>
+    <mergeCell ref="B82:E82"/>
+    <mergeCell ref="F82:H82"/>
+    <mergeCell ref="I82:J82"/>
+    <mergeCell ref="B83:E83"/>
+    <mergeCell ref="F83:H83"/>
+    <mergeCell ref="I83:J83"/>
+    <mergeCell ref="B74:E74"/>
+    <mergeCell ref="F74:H74"/>
+    <mergeCell ref="I74:J74"/>
+    <mergeCell ref="B75:E75"/>
+    <mergeCell ref="F75:H75"/>
+    <mergeCell ref="I75:J75"/>
+    <mergeCell ref="B79:E79"/>
+    <mergeCell ref="F79:H79"/>
+    <mergeCell ref="I79:J79"/>
+    <mergeCell ref="B89:J89"/>
+    <mergeCell ref="B91:E91"/>
+    <mergeCell ref="F91:H91"/>
+    <mergeCell ref="I91:J91"/>
+    <mergeCell ref="B81:E81"/>
+    <mergeCell ref="F81:H81"/>
+    <mergeCell ref="I81:J81"/>
+    <mergeCell ref="B61:J63"/>
+    <mergeCell ref="B65:J65"/>
+    <mergeCell ref="B77:J77"/>
+    <mergeCell ref="B67:E67"/>
+    <mergeCell ref="F67:H67"/>
+    <mergeCell ref="I67:J67"/>
+    <mergeCell ref="B69:E69"/>
+    <mergeCell ref="F69:H69"/>
+    <mergeCell ref="I69:J69"/>
+    <mergeCell ref="B72:E72"/>
+    <mergeCell ref="F72:H72"/>
+    <mergeCell ref="I72:J72"/>
+    <mergeCell ref="B73:E73"/>
+    <mergeCell ref="F73:H73"/>
+    <mergeCell ref="I73:J73"/>
+    <mergeCell ref="B70:E70"/>
+    <mergeCell ref="F70:H70"/>
+    <mergeCell ref="B50:D50"/>
+    <mergeCell ref="F50:I50"/>
+    <mergeCell ref="B51:J51"/>
+    <mergeCell ref="B52:J52"/>
+    <mergeCell ref="B53:J53"/>
+    <mergeCell ref="B59:J59"/>
+    <mergeCell ref="B14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="F26:H26"/>
+    <mergeCell ref="I26:J26"/>
+    <mergeCell ref="B47:D47"/>
+    <mergeCell ref="E47:I47"/>
+    <mergeCell ref="B46:E46"/>
+    <mergeCell ref="F46:H46"/>
+    <mergeCell ref="I46:J46"/>
+    <mergeCell ref="F44:H44"/>
+    <mergeCell ref="F45:H45"/>
+    <mergeCell ref="I41:J41"/>
+    <mergeCell ref="I42:J42"/>
+    <mergeCell ref="I43:J43"/>
+    <mergeCell ref="I44:J44"/>
+    <mergeCell ref="I45:J45"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="F38:H38"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="I22:J22"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="I29:J29"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="B44:E44"/>
+    <mergeCell ref="B45:E45"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="F20:H20"/>
+    <mergeCell ref="F21:H21"/>
+    <mergeCell ref="F22:H22"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="B40:E40"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B41:E41"/>
+    <mergeCell ref="B42:E42"/>
+    <mergeCell ref="B43:E43"/>
+    <mergeCell ref="B36:J36"/>
+    <mergeCell ref="B33:E33"/>
+    <mergeCell ref="B34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="F40:H40"/>
+    <mergeCell ref="F41:H41"/>
+    <mergeCell ref="F42:H42"/>
+    <mergeCell ref="F43:H43"/>
     <mergeCell ref="B6:J6"/>
     <mergeCell ref="B28:E28"/>
     <mergeCell ref="B29:E29"/>
@@ -2151,148 +2293,6 @@
     <mergeCell ref="B12:J12"/>
     <mergeCell ref="I16:J16"/>
     <mergeCell ref="B16:E16"/>
-    <mergeCell ref="B44:E44"/>
-    <mergeCell ref="B45:E45"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="F20:H20"/>
-    <mergeCell ref="F21:H21"/>
-    <mergeCell ref="F22:H22"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="B40:E40"/>
-    <mergeCell ref="B38:E38"/>
-    <mergeCell ref="B41:E41"/>
-    <mergeCell ref="B42:E42"/>
-    <mergeCell ref="B43:E43"/>
-    <mergeCell ref="B36:J36"/>
-    <mergeCell ref="B33:E33"/>
-    <mergeCell ref="B34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="F40:H40"/>
-    <mergeCell ref="F41:H41"/>
-    <mergeCell ref="F42:H42"/>
-    <mergeCell ref="F43:H43"/>
-    <mergeCell ref="I40:J40"/>
-    <mergeCell ref="F38:H38"/>
-    <mergeCell ref="I38:J38"/>
-    <mergeCell ref="I22:J22"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="I31:J31"/>
-    <mergeCell ref="B50:D50"/>
-    <mergeCell ref="F50:I50"/>
-    <mergeCell ref="B51:J51"/>
-    <mergeCell ref="B52:J52"/>
-    <mergeCell ref="B53:J53"/>
-    <mergeCell ref="B59:J59"/>
-    <mergeCell ref="B14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="F26:H26"/>
-    <mergeCell ref="I26:J26"/>
-    <mergeCell ref="B47:D47"/>
-    <mergeCell ref="E47:I47"/>
-    <mergeCell ref="B46:E46"/>
-    <mergeCell ref="F46:H46"/>
-    <mergeCell ref="I46:J46"/>
-    <mergeCell ref="F44:H44"/>
-    <mergeCell ref="F45:H45"/>
-    <mergeCell ref="I41:J41"/>
-    <mergeCell ref="I42:J42"/>
-    <mergeCell ref="I43:J43"/>
-    <mergeCell ref="I44:J44"/>
-    <mergeCell ref="I45:J45"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="B89:J89"/>
-    <mergeCell ref="B91:E91"/>
-    <mergeCell ref="F91:H91"/>
-    <mergeCell ref="I91:J91"/>
-    <mergeCell ref="B81:E81"/>
-    <mergeCell ref="F81:H81"/>
-    <mergeCell ref="I81:J81"/>
-    <mergeCell ref="B61:J63"/>
-    <mergeCell ref="B65:J65"/>
-    <mergeCell ref="B77:J77"/>
-    <mergeCell ref="B67:E67"/>
-    <mergeCell ref="F67:H67"/>
-    <mergeCell ref="I67:J67"/>
-    <mergeCell ref="B69:E69"/>
-    <mergeCell ref="F69:H69"/>
-    <mergeCell ref="I69:J69"/>
-    <mergeCell ref="B72:E72"/>
-    <mergeCell ref="F72:H72"/>
-    <mergeCell ref="I72:J72"/>
-    <mergeCell ref="B73:E73"/>
-    <mergeCell ref="F73:H73"/>
-    <mergeCell ref="I73:J73"/>
-    <mergeCell ref="B70:E70"/>
-    <mergeCell ref="F70:H70"/>
-    <mergeCell ref="I70:J70"/>
-    <mergeCell ref="B71:E71"/>
-    <mergeCell ref="F71:H71"/>
-    <mergeCell ref="I71:J71"/>
-    <mergeCell ref="B82:E82"/>
-    <mergeCell ref="F82:H82"/>
-    <mergeCell ref="I82:J82"/>
-    <mergeCell ref="B83:E83"/>
-    <mergeCell ref="F83:H83"/>
-    <mergeCell ref="I83:J83"/>
-    <mergeCell ref="B74:E74"/>
-    <mergeCell ref="F74:H74"/>
-    <mergeCell ref="I74:J74"/>
-    <mergeCell ref="B75:E75"/>
-    <mergeCell ref="F75:H75"/>
-    <mergeCell ref="I75:J75"/>
-    <mergeCell ref="B79:E79"/>
-    <mergeCell ref="F79:H79"/>
-    <mergeCell ref="I79:J79"/>
-    <mergeCell ref="B86:E86"/>
-    <mergeCell ref="F86:H86"/>
-    <mergeCell ref="I86:J86"/>
-    <mergeCell ref="B87:E87"/>
-    <mergeCell ref="F87:H87"/>
-    <mergeCell ref="I87:J87"/>
-    <mergeCell ref="B84:E84"/>
-    <mergeCell ref="F84:H84"/>
-    <mergeCell ref="I84:J84"/>
-    <mergeCell ref="B85:E85"/>
-    <mergeCell ref="F85:H85"/>
-    <mergeCell ref="I85:J85"/>
-    <mergeCell ref="B95:E95"/>
-    <mergeCell ref="F95:H95"/>
-    <mergeCell ref="I95:J95"/>
-    <mergeCell ref="B96:E96"/>
-    <mergeCell ref="F96:H96"/>
-    <mergeCell ref="I96:J96"/>
-    <mergeCell ref="B93:E93"/>
-    <mergeCell ref="F93:H93"/>
-    <mergeCell ref="I93:J93"/>
-    <mergeCell ref="B94:E94"/>
-    <mergeCell ref="F94:H94"/>
-    <mergeCell ref="I94:J94"/>
-    <mergeCell ref="B105:J105"/>
-    <mergeCell ref="B106:J106"/>
-    <mergeCell ref="B99:E99"/>
-    <mergeCell ref="F99:H99"/>
-    <mergeCell ref="I99:J99"/>
-    <mergeCell ref="B103:D103"/>
-    <mergeCell ref="F103:I103"/>
-    <mergeCell ref="B104:J104"/>
-    <mergeCell ref="B97:E97"/>
-    <mergeCell ref="F97:H97"/>
-    <mergeCell ref="I97:J97"/>
-    <mergeCell ref="B98:E98"/>
-    <mergeCell ref="F98:H98"/>
-    <mergeCell ref="I98:J98"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
